--- a/cha-bio-safety/public/templates/worklog_template.xlsx
+++ b/cha-bio-safety/public/templates/worklog_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05D78327-E7D4-4A9E-A501-978CB2EEB49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21A2DE1A-67EC-47DD-813C-52427B133CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="양식" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="126">
   <si>
     <t>■ 화재의 예방 및 안전관리에 관한 법률 시행규칙 [별지 제12서식]  </t>
   </si>
@@ -216,13 +216,13 @@
     <t>C4</t>
   </si>
   <si>
-    <t>현재 년 숫자</t>
+    <t>현재 년 yy</t>
   </si>
   <si>
     <t>E4</t>
   </si>
   <si>
-    <t>현재 월 숫자</t>
+    <t>현재 월 m</t>
   </si>
   <si>
     <t>G4</t>
@@ -234,7 +234,7 @@
     <t>M4</t>
   </si>
   <si>
-    <t>현재 월의 말일 숫자</t>
+    <t>현재 월의 말일 d</t>
   </si>
   <si>
     <t>U4</t>
@@ -258,10 +258,7 @@
     <t>소방 펌프 - 수동 기동 점검</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>C14</t>
+    <t>C17</t>
   </si>
   <si>
     <t>방화셔터 - 작동 상태 점검</t>
@@ -273,7 +270,7 @@
     <t>유도등 - 점등 상태, 전원 상태</t>
   </si>
   <si>
-    <t>C17</t>
+    <t>C24</t>
   </si>
   <si>
     <t>B1F - 직원식당</t>
@@ -282,7 +279,7 @@
     <t>B4F - 보일러</t>
   </si>
   <si>
-    <t>C24</t>
+    <t>C31</t>
   </si>
   <si>
     <t>수신기 정상유지</t>
@@ -318,18 +315,27 @@
     <t>Y26</t>
   </si>
   <si>
-    <t>"√" 삽입</t>
+    <t>화기취급감독 확인결과 양호 시 "√" 삽입</t>
   </si>
   <si>
     <t>Y28</t>
   </si>
   <si>
+    <t>화기취급감독 확인결과 불량 시 "√" 삽입</t>
+  </si>
+  <si>
     <t>Y33</t>
   </si>
   <si>
+    <t>기타사항 확인결과 양호 시 "√" 삽입</t>
+  </si>
+  <si>
     <t>Y35</t>
   </si>
   <si>
+    <t>기타사항 확인결과 불량 시 "√" 삽입</t>
+  </si>
+  <si>
     <t>AA10</t>
   </si>
   <si>
@@ -345,7 +351,79 @@
     <t>AA17</t>
   </si>
   <si>
+    <t>화기취급감독 조치사항 작성칸</t>
+  </si>
+  <si>
     <t>AA24</t>
+  </si>
+  <si>
+    <t>기타사항 조치사항 작성칸</t>
+  </si>
+  <si>
+    <t>C40</t>
+  </si>
+  <si>
+    <t>보고 일시 년 yy</t>
+  </si>
+  <si>
+    <t>E40</t>
+  </si>
+  <si>
+    <t>보고 일시 월 m</t>
+  </si>
+  <si>
+    <t>G40</t>
+  </si>
+  <si>
+    <t>보고 일시 일 d</t>
+  </si>
+  <si>
+    <t>K40</t>
+  </si>
+  <si>
+    <t>대면 체크 시 "√" 삽입</t>
+  </si>
+  <si>
+    <t>Q40</t>
+  </si>
+  <si>
+    <t>서면 체크 시 "√" 삽입</t>
+  </si>
+  <si>
+    <t>U40</t>
+  </si>
+  <si>
+    <t>정보통신 체크 시 "√" 삽입</t>
+  </si>
+  <si>
+    <t>K41</t>
+  </si>
+  <si>
+    <t>조치방법 이전 체크 시 "√" 삽입</t>
+  </si>
+  <si>
+    <t>Q41</t>
+  </si>
+  <si>
+    <t>조치방법 제거 체크 시 "√" 삽입</t>
+  </si>
+  <si>
+    <t>U41</t>
+  </si>
+  <si>
+    <t>조치방법 수리ㆍ교체 체크 시 "√" 삽입</t>
+  </si>
+  <si>
+    <t>Y41</t>
+  </si>
+  <si>
+    <t>조치방법 기타 체크 시 "√" 삽입</t>
+  </si>
+  <si>
+    <t>AA41</t>
+  </si>
+  <si>
+    <t>조치방법 기타 체크 시 기타 내역 작성칸</t>
   </si>
 </sst>
 </file>
@@ -355,7 +433,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,6 +502,12 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1289,7 +1373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1300,6 +1384,66 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1312,71 +1456,203 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -1384,51 +1660,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
@@ -1453,199 +1684,61 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2013,1203 +2106,1203 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:30">
-      <c r="B1" s="105" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="107"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="37"/>
       <c r="AD1" s="4"/>
     </row>
     <row r="2" spans="2:30" ht="26.25">
-      <c r="B2" s="108" t="s">
+      <c r="B2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="109"/>
-      <c r="S2" s="109"/>
-      <c r="T2" s="109"/>
-      <c r="U2" s="109"/>
-      <c r="V2" s="109"/>
-      <c r="W2" s="109"/>
-      <c r="X2" s="109"/>
-      <c r="Y2" s="109"/>
-      <c r="Z2" s="109"/>
-      <c r="AA2" s="109"/>
-      <c r="AB2" s="110"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+      <c r="W2" s="39"/>
+      <c r="X2" s="39"/>
+      <c r="Y2" s="39"/>
+      <c r="Z2" s="39"/>
+      <c r="AA2" s="39"/>
+      <c r="AB2" s="40"/>
     </row>
     <row r="3" spans="2:30">
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="112"/>
-      <c r="K3" s="112"/>
-      <c r="L3" s="112"/>
-      <c r="M3" s="112"/>
-      <c r="N3" s="112"/>
-      <c r="O3" s="112"/>
-      <c r="P3" s="112"/>
-      <c r="Q3" s="112"/>
-      <c r="R3" s="112"/>
-      <c r="S3" s="112"/>
-      <c r="T3" s="112"/>
-      <c r="U3" s="112"/>
-      <c r="V3" s="112"/>
-      <c r="W3" s="112"/>
-      <c r="X3" s="112"/>
-      <c r="Y3" s="112"/>
-      <c r="Z3" s="112"/>
-      <c r="AA3" s="112"/>
-      <c r="AB3" s="113"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
+      <c r="Y3" s="42"/>
+      <c r="Z3" s="42"/>
+      <c r="AA3" s="42"/>
+      <c r="AB3" s="43"/>
     </row>
     <row r="4" spans="2:30">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15" t="s">
+      <c r="E4" s="32"/>
+      <c r="F4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15" t="s">
+      <c r="G4" s="32"/>
+      <c r="H4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="12"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15" t="s">
+      <c r="J4" s="8"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="15"/>
-      <c r="N4" s="13" t="s">
+      <c r="M4" s="32"/>
+      <c r="N4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="114" t="s">
+      <c r="O4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="115"/>
-      <c r="Q4" s="115"/>
-      <c r="R4" s="115"/>
-      <c r="S4" s="115"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="117"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118"/>
-      <c r="X4" s="118"/>
-      <c r="Y4" s="118"/>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="15"/>
-      <c r="AB4" s="16" t="s">
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="33" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:30">
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="94" t="s">
+      <c r="C5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="94" t="s">
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="95"/>
-      <c r="K5" s="95"/>
-      <c r="L5" s="95"/>
-      <c r="M5" s="95"/>
-      <c r="N5" s="96"/>
-      <c r="O5" s="94" t="s">
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="P5" s="95"/>
-      <c r="Q5" s="95"/>
-      <c r="R5" s="95"/>
-      <c r="S5" s="95"/>
-      <c r="T5" s="97"/>
-      <c r="U5" s="119" t="s">
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="50"/>
+      <c r="U5" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="V5" s="119"/>
-      <c r="W5" s="119"/>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="119"/>
-      <c r="Z5" s="119"/>
-      <c r="AA5" s="119"/>
-      <c r="AB5" s="120"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="53"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="53"/>
+      <c r="AB5" s="54"/>
     </row>
     <row r="6" spans="2:30">
-      <c r="B6" s="40"/>
-      <c r="C6" s="81" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="81" t="s">
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="N6" s="82"/>
-      <c r="O6" s="82"/>
-      <c r="P6" s="82"/>
-      <c r="Q6" s="82"/>
-      <c r="R6" s="82"/>
-      <c r="S6" s="82"/>
-      <c r="T6" s="82"/>
-      <c r="U6" s="82"/>
-      <c r="V6" s="82"/>
-      <c r="W6" s="82"/>
-      <c r="X6" s="82"/>
-      <c r="Y6" s="82"/>
-      <c r="Z6" s="82"/>
-      <c r="AA6" s="82"/>
-      <c r="AB6" s="83"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="56"/>
+      <c r="T6" s="56"/>
+      <c r="U6" s="56"/>
+      <c r="V6" s="56"/>
+      <c r="W6" s="56"/>
+      <c r="X6" s="56"/>
+      <c r="Y6" s="56"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="57"/>
     </row>
     <row r="7" spans="2:30">
-      <c r="B7" s="40"/>
-      <c r="C7" s="81" t="s">
+      <c r="B7" s="89"/>
+      <c r="C7" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="81" t="s">
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="103" t="s">
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="N7" s="82"/>
-      <c r="O7" s="82"/>
-      <c r="P7" s="82"/>
-      <c r="Q7" s="82"/>
-      <c r="R7" s="82"/>
-      <c r="S7" s="82"/>
-      <c r="T7" s="83"/>
-      <c r="U7" s="82" t="s">
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="57"/>
+      <c r="U7" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="V7" s="82"/>
-      <c r="W7" s="82"/>
-      <c r="X7" s="82"/>
-      <c r="Y7" s="104"/>
-      <c r="Z7" s="81" t="s">
+      <c r="V7" s="56"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="56"/>
+      <c r="Y7" s="59"/>
+      <c r="Z7" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="AA7" s="82"/>
-      <c r="AB7" s="83"/>
+      <c r="AA7" s="56"/>
+      <c r="AB7" s="57"/>
     </row>
     <row r="8" spans="2:30">
-      <c r="B8" s="41"/>
-      <c r="C8" s="92">
+      <c r="B8" s="90"/>
+      <c r="C8" s="60">
         <v>5</v>
       </c>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="92">
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="60">
         <v>8</v>
       </c>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="99">
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63">
         <v>60557.82</v>
       </c>
-      <c r="N8" s="100"/>
-      <c r="O8" s="100"/>
-      <c r="P8" s="100"/>
-      <c r="Q8" s="100"/>
-      <c r="R8" s="100"/>
-      <c r="S8" s="100"/>
-      <c r="T8" s="101"/>
-      <c r="U8" s="100">
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="64">
         <v>6131.87</v>
       </c>
-      <c r="V8" s="100"/>
-      <c r="W8" s="100"/>
-      <c r="X8" s="100"/>
-      <c r="Y8" s="102"/>
-      <c r="Z8" s="92">
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="66"/>
+      <c r="Z8" s="60">
         <v>1</v>
       </c>
-      <c r="AA8" s="93"/>
-      <c r="AB8" s="98"/>
+      <c r="AA8" s="61"/>
+      <c r="AB8" s="62"/>
     </row>
     <row r="9" spans="2:30">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="94" t="s">
+      <c r="C9" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="95"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="95"/>
-      <c r="M9" s="95"/>
-      <c r="N9" s="95"/>
-      <c r="O9" s="95"/>
-      <c r="P9" s="95"/>
-      <c r="Q9" s="95"/>
-      <c r="R9" s="95"/>
-      <c r="S9" s="95"/>
-      <c r="T9" s="95"/>
-      <c r="U9" s="95"/>
-      <c r="V9" s="95"/>
-      <c r="W9" s="96"/>
-      <c r="X9" s="94" t="s">
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
+      <c r="V9" s="45"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="Y9" s="95"/>
-      <c r="Z9" s="96"/>
-      <c r="AA9" s="94" t="s">
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="46"/>
+      <c r="AA9" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AB9" s="97"/>
+      <c r="AB9" s="50"/>
     </row>
     <row r="10" spans="2:30">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="89"/>
-      <c r="J10" s="89"/>
-      <c r="K10" s="89"/>
-      <c r="L10" s="89"/>
-      <c r="M10" s="89"/>
-      <c r="N10" s="89"/>
-      <c r="O10" s="89"/>
-      <c r="P10" s="89"/>
-      <c r="Q10" s="89"/>
-      <c r="R10" s="89"/>
-      <c r="S10" s="89"/>
-      <c r="T10" s="89"/>
-      <c r="U10" s="89"/>
-      <c r="V10" s="89"/>
-      <c r="W10" s="89"/>
-      <c r="X10" s="18"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="63" t="s">
+      <c r="D10" s="107"/>
+      <c r="E10" s="107"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="107"/>
+      <c r="I10" s="107"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="107"/>
+      <c r="L10" s="107"/>
+      <c r="M10" s="107"/>
+      <c r="N10" s="107"/>
+      <c r="O10" s="107"/>
+      <c r="P10" s="107"/>
+      <c r="Q10" s="107"/>
+      <c r="R10" s="107"/>
+      <c r="S10" s="107"/>
+      <c r="T10" s="107"/>
+      <c r="U10" s="107"/>
+      <c r="V10" s="107"/>
+      <c r="W10" s="107"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
+      <c r="AA10" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="AB10" s="64"/>
+      <c r="AB10" s="117"/>
     </row>
     <row r="11" spans="2:30">
-      <c r="B11" s="43"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="91"/>
-      <c r="K11" s="91"/>
-      <c r="L11" s="91"/>
-      <c r="M11" s="91"/>
-      <c r="N11" s="91"/>
-      <c r="O11" s="91"/>
-      <c r="P11" s="91"/>
-      <c r="Q11" s="91"/>
-      <c r="R11" s="91"/>
-      <c r="S11" s="91"/>
-      <c r="T11" s="91"/>
-      <c r="U11" s="91"/>
-      <c r="V11" s="91"/>
-      <c r="W11" s="91"/>
-      <c r="X11" s="18"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="65"/>
-      <c r="AB11" s="66"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="109"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="109"/>
+      <c r="J11" s="109"/>
+      <c r="K11" s="109"/>
+      <c r="L11" s="109"/>
+      <c r="M11" s="109"/>
+      <c r="N11" s="109"/>
+      <c r="O11" s="109"/>
+      <c r="P11" s="109"/>
+      <c r="Q11" s="109"/>
+      <c r="R11" s="109"/>
+      <c r="S11" s="109"/>
+      <c r="T11" s="109"/>
+      <c r="U11" s="109"/>
+      <c r="V11" s="109"/>
+      <c r="W11" s="109"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="118"/>
+      <c r="AB11" s="119"/>
     </row>
     <row r="12" spans="2:30">
-      <c r="B12" s="43"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="58"/>
-      <c r="S12" s="58"/>
-      <c r="T12" s="58"/>
-      <c r="U12" s="58"/>
-      <c r="V12" s="58"/>
-      <c r="W12" s="58"/>
-      <c r="X12" s="20" t="s">
+      <c r="B12" s="92"/>
+      <c r="C12" s="110"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="111"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="111"/>
+      <c r="S12" s="111"/>
+      <c r="T12" s="111"/>
+      <c r="U12" s="111"/>
+      <c r="V12" s="111"/>
+      <c r="W12" s="111"/>
+      <c r="X12" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19" t="s">
+      <c r="Y12" s="12"/>
+      <c r="Z12" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AA12" s="65"/>
-      <c r="AB12" s="66"/>
+      <c r="AA12" s="118"/>
+      <c r="AB12" s="119"/>
     </row>
     <row r="13" spans="2:30">
-      <c r="B13" s="43"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="58"/>
-      <c r="V13" s="58"/>
-      <c r="W13" s="58"/>
-      <c r="X13" s="20"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="65"/>
-      <c r="AB13" s="66"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="111"/>
+      <c r="S13" s="111"/>
+      <c r="T13" s="111"/>
+      <c r="U13" s="111"/>
+      <c r="V13" s="111"/>
+      <c r="W13" s="111"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
+      <c r="AA13" s="118"/>
+      <c r="AB13" s="119"/>
     </row>
     <row r="14" spans="2:30">
-      <c r="B14" s="43"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="58"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="58"/>
-      <c r="S14" s="58"/>
-      <c r="T14" s="58"/>
-      <c r="U14" s="58"/>
-      <c r="V14" s="58"/>
-      <c r="W14" s="58"/>
-      <c r="X14" s="20" t="s">
+      <c r="B14" s="92"/>
+      <c r="C14" s="110"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111"/>
+      <c r="S14" s="111"/>
+      <c r="T14" s="111"/>
+      <c r="U14" s="111"/>
+      <c r="V14" s="111"/>
+      <c r="W14" s="111"/>
+      <c r="X14" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="21" t="s">
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="AA14" s="65"/>
-      <c r="AB14" s="66"/>
+      <c r="AA14" s="118"/>
+      <c r="AB14" s="119"/>
     </row>
     <row r="15" spans="2:30">
-      <c r="B15" s="43"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="58"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="58"/>
-      <c r="R15" s="58"/>
-      <c r="S15" s="58"/>
-      <c r="T15" s="58"/>
-      <c r="U15" s="58"/>
-      <c r="V15" s="58"/>
-      <c r="W15" s="58"/>
-      <c r="X15" s="20"/>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="65"/>
-      <c r="AB15" s="66"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="111"/>
+      <c r="S15" s="111"/>
+      <c r="T15" s="111"/>
+      <c r="U15" s="111"/>
+      <c r="V15" s="111"/>
+      <c r="W15" s="111"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="14"/>
+      <c r="AA15" s="118"/>
+      <c r="AB15" s="119"/>
     </row>
     <row r="16" spans="2:30">
-      <c r="B16" s="44"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="58"/>
-      <c r="O16" s="58"/>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="58"/>
-      <c r="T16" s="58"/>
-      <c r="U16" s="58"/>
-      <c r="V16" s="58"/>
-      <c r="W16" s="58"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="23"/>
-      <c r="AA16" s="78"/>
-      <c r="AB16" s="80"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="111"/>
+      <c r="S16" s="111"/>
+      <c r="T16" s="111"/>
+      <c r="U16" s="111"/>
+      <c r="V16" s="111"/>
+      <c r="W16" s="111"/>
+      <c r="X16" s="15"/>
+      <c r="Y16" s="16"/>
+      <c r="Z16" s="16"/>
+      <c r="AA16" s="120"/>
+      <c r="AB16" s="121"/>
     </row>
     <row r="17" spans="2:28">
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="58"/>
-      <c r="T17" s="58"/>
-      <c r="U17" s="58"/>
-      <c r="V17" s="58"/>
-      <c r="W17" s="58"/>
-      <c r="X17" s="18"/>
-      <c r="Y17" s="19"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="63" t="s">
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="111"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="111"/>
+      <c r="N17" s="111"/>
+      <c r="O17" s="111"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="111"/>
+      <c r="S17" s="111"/>
+      <c r="T17" s="111"/>
+      <c r="U17" s="111"/>
+      <c r="V17" s="111"/>
+      <c r="W17" s="111"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="12"/>
+      <c r="Z17" s="12"/>
+      <c r="AA17" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="AB17" s="64"/>
+      <c r="AB17" s="117"/>
     </row>
     <row r="18" spans="2:28">
-      <c r="B18" s="43"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="58"/>
-      <c r="T18" s="58"/>
-      <c r="U18" s="58"/>
-      <c r="V18" s="58"/>
-      <c r="W18" s="58"/>
-      <c r="X18" s="18"/>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="65"/>
-      <c r="AB18" s="66"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="111"/>
+      <c r="M18" s="111"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="111"/>
+      <c r="S18" s="111"/>
+      <c r="T18" s="111"/>
+      <c r="U18" s="111"/>
+      <c r="V18" s="111"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
+      <c r="AA18" s="118"/>
+      <c r="AB18" s="119"/>
     </row>
     <row r="19" spans="2:28">
-      <c r="B19" s="43"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="58"/>
-      <c r="T19" s="58"/>
-      <c r="U19" s="58"/>
-      <c r="V19" s="58"/>
-      <c r="W19" s="58"/>
-      <c r="X19" s="20" t="s">
+      <c r="B19" s="92"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="111"/>
+      <c r="N19" s="111"/>
+      <c r="O19" s="111"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="111"/>
+      <c r="R19" s="111"/>
+      <c r="S19" s="111"/>
+      <c r="T19" s="111"/>
+      <c r="U19" s="111"/>
+      <c r="V19" s="111"/>
+      <c r="W19" s="111"/>
+      <c r="X19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19" t="s">
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AA19" s="65"/>
-      <c r="AB19" s="66"/>
+      <c r="AA19" s="118"/>
+      <c r="AB19" s="119"/>
     </row>
     <row r="20" spans="2:28">
-      <c r="B20" s="43"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
-      <c r="P20" s="58"/>
-      <c r="Q20" s="58"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="58"/>
-      <c r="T20" s="58"/>
-      <c r="U20" s="58"/>
-      <c r="V20" s="58"/>
-      <c r="W20" s="58"/>
-      <c r="X20" s="20"/>
-      <c r="Y20" s="19"/>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="65"/>
-      <c r="AB20" s="66"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="111"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="111"/>
+      <c r="S20" s="111"/>
+      <c r="T20" s="111"/>
+      <c r="U20" s="111"/>
+      <c r="V20" s="111"/>
+      <c r="W20" s="111"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+      <c r="AA20" s="118"/>
+      <c r="AB20" s="119"/>
     </row>
     <row r="21" spans="2:28">
-      <c r="B21" s="43"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
-      <c r="O21" s="58"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="58"/>
-      <c r="R21" s="58"/>
-      <c r="S21" s="58"/>
-      <c r="T21" s="58"/>
-      <c r="U21" s="58"/>
-      <c r="V21" s="58"/>
-      <c r="W21" s="58"/>
-      <c r="X21" s="20" t="s">
+      <c r="B21" s="92"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="111"/>
+      <c r="N21" s="111"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="111"/>
+      <c r="R21" s="111"/>
+      <c r="S21" s="111"/>
+      <c r="T21" s="111"/>
+      <c r="U21" s="111"/>
+      <c r="V21" s="111"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Y21" s="19"/>
-      <c r="Z21" s="21" t="s">
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="AA21" s="65"/>
-      <c r="AB21" s="66"/>
+      <c r="AA21" s="118"/>
+      <c r="AB21" s="119"/>
     </row>
     <row r="22" spans="2:28">
-      <c r="B22" s="43"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="58"/>
-      <c r="S22" s="58"/>
-      <c r="T22" s="58"/>
-      <c r="U22" s="58"/>
-      <c r="V22" s="58"/>
-      <c r="W22" s="58"/>
-      <c r="X22" s="20"/>
-      <c r="Y22" s="19"/>
-      <c r="Z22" s="21"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="66"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="111"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="111"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="111"/>
+      <c r="S22" s="111"/>
+      <c r="T22" s="111"/>
+      <c r="U22" s="111"/>
+      <c r="V22" s="111"/>
+      <c r="W22" s="111"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="118"/>
+      <c r="AB22" s="119"/>
     </row>
     <row r="23" spans="2:28">
-      <c r="B23" s="44"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
-      <c r="O23" s="58"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="58"/>
-      <c r="S23" s="58"/>
-      <c r="T23" s="58"/>
-      <c r="U23" s="58"/>
-      <c r="V23" s="58"/>
-      <c r="W23" s="58"/>
-      <c r="X23" s="22"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="23"/>
-      <c r="AA23" s="78"/>
-      <c r="AB23" s="80"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="111"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="111"/>
+      <c r="N23" s="111"/>
+      <c r="O23" s="111"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="111"/>
+      <c r="R23" s="111"/>
+      <c r="S23" s="111"/>
+      <c r="T23" s="111"/>
+      <c r="U23" s="111"/>
+      <c r="V23" s="111"/>
+      <c r="W23" s="111"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="16"/>
+      <c r="Z23" s="16"/>
+      <c r="AA23" s="120"/>
+      <c r="AB23" s="121"/>
     </row>
     <row r="24" spans="2:28">
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="57" t="s">
+      <c r="C24" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
-      <c r="P24" s="58"/>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="58"/>
-      <c r="S24" s="58"/>
-      <c r="T24" s="58"/>
-      <c r="U24" s="58"/>
-      <c r="V24" s="58"/>
-      <c r="W24" s="58"/>
-      <c r="X24" s="18"/>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="63" t="s">
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="111"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="111"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="111"/>
+      <c r="S24" s="111"/>
+      <c r="T24" s="111"/>
+      <c r="U24" s="111"/>
+      <c r="V24" s="111"/>
+      <c r="W24" s="111"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="12"/>
+      <c r="Z24" s="12"/>
+      <c r="AA24" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="AB24" s="64"/>
+      <c r="AB24" s="117"/>
     </row>
     <row r="25" spans="2:28">
-      <c r="B25" s="43"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="58"/>
-      <c r="T25" s="58"/>
-      <c r="U25" s="58"/>
-      <c r="V25" s="58"/>
-      <c r="W25" s="58"/>
-      <c r="X25" s="18"/>
-      <c r="Y25" s="19"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="65"/>
-      <c r="AB25" s="66"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="111"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111"/>
+      <c r="R25" s="111"/>
+      <c r="S25" s="111"/>
+      <c r="T25" s="111"/>
+      <c r="U25" s="111"/>
+      <c r="V25" s="111"/>
+      <c r="W25" s="111"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="12"/>
+      <c r="Z25" s="12"/>
+      <c r="AA25" s="118"/>
+      <c r="AB25" s="119"/>
     </row>
     <row r="26" spans="2:28">
-      <c r="B26" s="43"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="58"/>
-      <c r="S26" s="58"/>
-      <c r="T26" s="58"/>
-      <c r="U26" s="58"/>
-      <c r="V26" s="58"/>
-      <c r="W26" s="58"/>
-      <c r="X26" s="20" t="s">
+      <c r="B26" s="92"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="111"/>
+      <c r="L26" s="111"/>
+      <c r="M26" s="111"/>
+      <c r="N26" s="111"/>
+      <c r="O26" s="111"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="111"/>
+      <c r="S26" s="111"/>
+      <c r="T26" s="111"/>
+      <c r="U26" s="111"/>
+      <c r="V26" s="111"/>
+      <c r="W26" s="111"/>
+      <c r="X26" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Y26" s="19"/>
-      <c r="Z26" s="19" t="s">
+      <c r="Y26" s="12"/>
+      <c r="Z26" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AA26" s="65"/>
-      <c r="AB26" s="66"/>
+      <c r="AA26" s="118"/>
+      <c r="AB26" s="119"/>
     </row>
     <row r="27" spans="2:28">
-      <c r="B27" s="43"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
-      <c r="P27" s="58"/>
-      <c r="Q27" s="58"/>
-      <c r="R27" s="58"/>
-      <c r="S27" s="58"/>
-      <c r="T27" s="58"/>
-      <c r="U27" s="58"/>
-      <c r="V27" s="58"/>
-      <c r="W27" s="58"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="19"/>
-      <c r="Z27" s="19"/>
-      <c r="AA27" s="65"/>
-      <c r="AB27" s="66"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="111"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="111"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="111"/>
+      <c r="N27" s="111"/>
+      <c r="O27" s="111"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="111"/>
+      <c r="R27" s="111"/>
+      <c r="S27" s="111"/>
+      <c r="T27" s="111"/>
+      <c r="U27" s="111"/>
+      <c r="V27" s="111"/>
+      <c r="W27" s="111"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="12"/>
+      <c r="Z27" s="12"/>
+      <c r="AA27" s="118"/>
+      <c r="AB27" s="119"/>
     </row>
     <row r="28" spans="2:28">
-      <c r="B28" s="43"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
-      <c r="P28" s="58"/>
-      <c r="Q28" s="58"/>
-      <c r="R28" s="58"/>
-      <c r="S28" s="58"/>
-      <c r="T28" s="58"/>
-      <c r="U28" s="58"/>
-      <c r="V28" s="58"/>
-      <c r="W28" s="58"/>
-      <c r="X28" s="20" t="s">
+      <c r="B28" s="92"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="111"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="111"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="111"/>
+      <c r="N28" s="111"/>
+      <c r="O28" s="111"/>
+      <c r="P28" s="111"/>
+      <c r="Q28" s="111"/>
+      <c r="R28" s="111"/>
+      <c r="S28" s="111"/>
+      <c r="T28" s="111"/>
+      <c r="U28" s="111"/>
+      <c r="V28" s="111"/>
+      <c r="W28" s="111"/>
+      <c r="X28" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Y28" s="19"/>
-      <c r="Z28" s="21" t="s">
+      <c r="Y28" s="12"/>
+      <c r="Z28" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="AA28" s="65"/>
-      <c r="AB28" s="66"/>
+      <c r="AA28" s="118"/>
+      <c r="AB28" s="119"/>
     </row>
     <row r="29" spans="2:28">
-      <c r="B29" s="43"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="58"/>
-      <c r="R29" s="58"/>
-      <c r="S29" s="58"/>
-      <c r="T29" s="58"/>
-      <c r="U29" s="58"/>
-      <c r="V29" s="58"/>
-      <c r="W29" s="58"/>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="19"/>
-      <c r="Z29" s="21"/>
-      <c r="AA29" s="65"/>
-      <c r="AB29" s="66"/>
+      <c r="B29" s="92"/>
+      <c r="C29" s="110"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="111"/>
+      <c r="F29" s="111"/>
+      <c r="G29" s="111"/>
+      <c r="H29" s="111"/>
+      <c r="I29" s="111"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="111"/>
+      <c r="L29" s="111"/>
+      <c r="M29" s="111"/>
+      <c r="N29" s="111"/>
+      <c r="O29" s="111"/>
+      <c r="P29" s="111"/>
+      <c r="Q29" s="111"/>
+      <c r="R29" s="111"/>
+      <c r="S29" s="111"/>
+      <c r="T29" s="111"/>
+      <c r="U29" s="111"/>
+      <c r="V29" s="111"/>
+      <c r="W29" s="111"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="12"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="118"/>
+      <c r="AB29" s="119"/>
     </row>
     <row r="30" spans="2:28">
-      <c r="B30" s="44"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="58"/>
-      <c r="O30" s="58"/>
-      <c r="P30" s="58"/>
-      <c r="Q30" s="58"/>
-      <c r="R30" s="58"/>
-      <c r="S30" s="58"/>
-      <c r="T30" s="58"/>
-      <c r="U30" s="58"/>
-      <c r="V30" s="58"/>
-      <c r="W30" s="58"/>
-      <c r="X30" s="22"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="23"/>
-      <c r="AA30" s="78"/>
-      <c r="AB30" s="80"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="110"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="111"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="111"/>
+      <c r="H30" s="111"/>
+      <c r="I30" s="111"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="111"/>
+      <c r="N30" s="111"/>
+      <c r="O30" s="111"/>
+      <c r="P30" s="111"/>
+      <c r="Q30" s="111"/>
+      <c r="R30" s="111"/>
+      <c r="S30" s="111"/>
+      <c r="T30" s="111"/>
+      <c r="U30" s="111"/>
+      <c r="V30" s="111"/>
+      <c r="W30" s="111"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="16"/>
+      <c r="Z30" s="16"/>
+      <c r="AA30" s="120"/>
+      <c r="AB30" s="121"/>
     </row>
     <row r="31" spans="2:28">
-      <c r="B31" s="42" t="s">
+      <c r="B31" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="58"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="58"/>
-      <c r="V31" s="58"/>
-      <c r="W31" s="58"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="10"/>
-      <c r="Z31" s="10"/>
-      <c r="AA31" s="63" t="s">
+      <c r="D31" s="111"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="111"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="111"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="111"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="111"/>
+      <c r="N31" s="111"/>
+      <c r="O31" s="111"/>
+      <c r="P31" s="111"/>
+      <c r="Q31" s="111"/>
+      <c r="R31" s="111"/>
+      <c r="S31" s="111"/>
+      <c r="T31" s="111"/>
+      <c r="U31" s="111"/>
+      <c r="V31" s="111"/>
+      <c r="W31" s="111"/>
+      <c r="X31" s="11"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="AB31" s="64"/>
+      <c r="AB31" s="117"/>
     </row>
     <row r="32" spans="2:28">
-      <c r="B32" s="43"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="58"/>
-      <c r="N32" s="58"/>
-      <c r="O32" s="58"/>
-      <c r="P32" s="58"/>
-      <c r="Q32" s="58"/>
-      <c r="R32" s="58"/>
-      <c r="S32" s="58"/>
-      <c r="T32" s="58"/>
-      <c r="U32" s="58"/>
-      <c r="V32" s="58"/>
-      <c r="W32" s="58"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="10"/>
-      <c r="Z32" s="10"/>
-      <c r="AA32" s="65"/>
-      <c r="AB32" s="66"/>
+      <c r="B32" s="92"/>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="111"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="111"/>
+      <c r="H32" s="111"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="111"/>
+      <c r="L32" s="111"/>
+      <c r="M32" s="111"/>
+      <c r="N32" s="111"/>
+      <c r="O32" s="111"/>
+      <c r="P32" s="111"/>
+      <c r="Q32" s="111"/>
+      <c r="R32" s="111"/>
+      <c r="S32" s="111"/>
+      <c r="T32" s="111"/>
+      <c r="U32" s="111"/>
+      <c r="V32" s="111"/>
+      <c r="W32" s="111"/>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="118"/>
+      <c r="AB32" s="119"/>
     </row>
     <row r="33" spans="2:28">
-      <c r="B33" s="43"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="58"/>
-      <c r="O33" s="58"/>
-      <c r="P33" s="58"/>
-      <c r="Q33" s="58"/>
-      <c r="R33" s="58"/>
-      <c r="S33" s="58"/>
-      <c r="T33" s="58"/>
-      <c r="U33" s="58"/>
-      <c r="V33" s="58"/>
-      <c r="W33" s="58"/>
-      <c r="X33" s="20" t="s">
+      <c r="B33" s="92"/>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="111"/>
+      <c r="F33" s="111"/>
+      <c r="G33" s="111"/>
+      <c r="H33" s="111"/>
+      <c r="I33" s="111"/>
+      <c r="J33" s="111"/>
+      <c r="K33" s="111"/>
+      <c r="L33" s="111"/>
+      <c r="M33" s="111"/>
+      <c r="N33" s="111"/>
+      <c r="O33" s="111"/>
+      <c r="P33" s="111"/>
+      <c r="Q33" s="111"/>
+      <c r="R33" s="111"/>
+      <c r="S33" s="111"/>
+      <c r="T33" s="111"/>
+      <c r="U33" s="111"/>
+      <c r="V33" s="111"/>
+      <c r="W33" s="111"/>
+      <c r="X33" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Y33" s="10"/>
-      <c r="Z33" s="10" t="s">
+      <c r="Y33" s="6"/>
+      <c r="Z33" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AA33" s="65"/>
-      <c r="AB33" s="66"/>
+      <c r="AA33" s="118"/>
+      <c r="AB33" s="119"/>
     </row>
     <row r="34" spans="2:28">
-      <c r="B34" s="43"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="58"/>
-      <c r="M34" s="58"/>
-      <c r="N34" s="58"/>
-      <c r="O34" s="58"/>
-      <c r="P34" s="58"/>
-      <c r="Q34" s="58"/>
-      <c r="R34" s="58"/>
-      <c r="S34" s="58"/>
-      <c r="T34" s="58"/>
-      <c r="U34" s="58"/>
-      <c r="V34" s="58"/>
-      <c r="W34" s="58"/>
-      <c r="X34" s="20"/>
-      <c r="Y34" s="10"/>
-      <c r="Z34" s="10"/>
-      <c r="AA34" s="65"/>
-      <c r="AB34" s="66"/>
+      <c r="B34" s="92"/>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
+      <c r="F34" s="111"/>
+      <c r="G34" s="111"/>
+      <c r="H34" s="111"/>
+      <c r="I34" s="111"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="111"/>
+      <c r="L34" s="111"/>
+      <c r="M34" s="111"/>
+      <c r="N34" s="111"/>
+      <c r="O34" s="111"/>
+      <c r="P34" s="111"/>
+      <c r="Q34" s="111"/>
+      <c r="R34" s="111"/>
+      <c r="S34" s="111"/>
+      <c r="T34" s="111"/>
+      <c r="U34" s="111"/>
+      <c r="V34" s="111"/>
+      <c r="W34" s="111"/>
+      <c r="X34" s="13"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="118"/>
+      <c r="AB34" s="119"/>
     </row>
     <row r="35" spans="2:28">
-      <c r="B35" s="43"/>
-      <c r="C35" s="57"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="58"/>
-      <c r="N35" s="58"/>
-      <c r="O35" s="58"/>
-      <c r="P35" s="58"/>
-      <c r="Q35" s="58"/>
-      <c r="R35" s="58"/>
-      <c r="S35" s="58"/>
-      <c r="T35" s="58"/>
-      <c r="U35" s="58"/>
-      <c r="V35" s="58"/>
-      <c r="W35" s="58"/>
-      <c r="X35" s="20" t="s">
+      <c r="B35" s="92"/>
+      <c r="C35" s="110"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="111"/>
+      <c r="F35" s="111"/>
+      <c r="G35" s="111"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="111"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="111"/>
+      <c r="L35" s="111"/>
+      <c r="M35" s="111"/>
+      <c r="N35" s="111"/>
+      <c r="O35" s="111"/>
+      <c r="P35" s="111"/>
+      <c r="Q35" s="111"/>
+      <c r="R35" s="111"/>
+      <c r="S35" s="111"/>
+      <c r="T35" s="111"/>
+      <c r="U35" s="111"/>
+      <c r="V35" s="111"/>
+      <c r="W35" s="111"/>
+      <c r="X35" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Y35" s="10"/>
-      <c r="Z35" s="24" t="s">
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="AA35" s="65"/>
-      <c r="AB35" s="66"/>
+      <c r="AA35" s="118"/>
+      <c r="AB35" s="119"/>
     </row>
     <row r="36" spans="2:28">
-      <c r="B36" s="43"/>
-      <c r="C36" s="59"/>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="60"/>
-      <c r="G36" s="60"/>
-      <c r="H36" s="60"/>
-      <c r="I36" s="60"/>
-      <c r="J36" s="60"/>
-      <c r="K36" s="60"/>
-      <c r="L36" s="60"/>
-      <c r="M36" s="60"/>
-      <c r="N36" s="60"/>
-      <c r="O36" s="60"/>
-      <c r="P36" s="60"/>
-      <c r="Q36" s="60"/>
-      <c r="R36" s="60"/>
-      <c r="S36" s="60"/>
-      <c r="T36" s="60"/>
-      <c r="U36" s="60"/>
-      <c r="V36" s="60"/>
-      <c r="W36" s="60"/>
-      <c r="X36" s="20"/>
-      <c r="Y36" s="10"/>
-      <c r="Z36" s="24"/>
-      <c r="AA36" s="65"/>
-      <c r="AB36" s="66"/>
+      <c r="B36" s="92"/>
+      <c r="C36" s="112"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="113"/>
+      <c r="H36" s="113"/>
+      <c r="I36" s="113"/>
+      <c r="J36" s="113"/>
+      <c r="K36" s="113"/>
+      <c r="L36" s="113"/>
+      <c r="M36" s="113"/>
+      <c r="N36" s="113"/>
+      <c r="O36" s="113"/>
+      <c r="P36" s="113"/>
+      <c r="Q36" s="113"/>
+      <c r="R36" s="113"/>
+      <c r="S36" s="113"/>
+      <c r="T36" s="113"/>
+      <c r="U36" s="113"/>
+      <c r="V36" s="113"/>
+      <c r="W36" s="113"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="6"/>
+      <c r="Z36" s="17"/>
+      <c r="AA36" s="118"/>
+      <c r="AB36" s="119"/>
     </row>
     <row r="37" spans="2:28">
-      <c r="B37" s="45"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="62"/>
-      <c r="E37" s="62"/>
-      <c r="F37" s="62"/>
-      <c r="G37" s="62"/>
-      <c r="H37" s="62"/>
-      <c r="I37" s="62"/>
-      <c r="J37" s="62"/>
-      <c r="K37" s="62"/>
-      <c r="L37" s="62"/>
-      <c r="M37" s="62"/>
-      <c r="N37" s="62"/>
-      <c r="O37" s="62"/>
-      <c r="P37" s="62"/>
-      <c r="Q37" s="62"/>
-      <c r="R37" s="62"/>
-      <c r="S37" s="62"/>
-      <c r="T37" s="62"/>
-      <c r="U37" s="62"/>
-      <c r="V37" s="62"/>
-      <c r="W37" s="62"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="10"/>
-      <c r="Z37" s="10"/>
-      <c r="AA37" s="67"/>
-      <c r="AB37" s="68"/>
+      <c r="B37" s="94"/>
+      <c r="C37" s="114"/>
+      <c r="D37" s="115"/>
+      <c r="E37" s="115"/>
+      <c r="F37" s="115"/>
+      <c r="G37" s="115"/>
+      <c r="H37" s="115"/>
+      <c r="I37" s="115"/>
+      <c r="J37" s="115"/>
+      <c r="K37" s="115"/>
+      <c r="L37" s="115"/>
+      <c r="M37" s="115"/>
+      <c r="N37" s="115"/>
+      <c r="O37" s="115"/>
+      <c r="P37" s="115"/>
+      <c r="Q37" s="115"/>
+      <c r="R37" s="115"/>
+      <c r="S37" s="115"/>
+      <c r="T37" s="115"/>
+      <c r="U37" s="115"/>
+      <c r="V37" s="115"/>
+      <c r="W37" s="115"/>
+      <c r="X37" s="11"/>
+      <c r="Y37" s="6"/>
+      <c r="Z37" s="6"/>
+      <c r="AA37" s="122"/>
+      <c r="AB37" s="123"/>
     </row>
     <row r="38" spans="2:28">
-      <c r="B38" s="39" t="s">
+      <c r="B38" s="88" t="s">
         <v>32</v>
       </c>
       <c r="C38" s="69" t="s">
@@ -3236,7 +3329,7 @@
       <c r="T38" s="76"/>
       <c r="U38" s="76"/>
       <c r="V38" s="76"/>
-      <c r="W38" s="84"/>
+      <c r="W38" s="79"/>
       <c r="X38" s="75" t="s">
         <v>35</v>
       </c>
@@ -3246,7 +3339,7 @@
       <c r="AB38" s="77"/>
     </row>
     <row r="39" spans="2:28">
-      <c r="B39" s="40"/>
+      <c r="B39" s="89"/>
       <c r="C39" s="72"/>
       <c r="D39" s="73"/>
       <c r="E39" s="73"/>
@@ -3254,135 +3347,135 @@
       <c r="G39" s="73"/>
       <c r="H39" s="73"/>
       <c r="I39" s="74"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="86"/>
-      <c r="L39" s="86"/>
-      <c r="M39" s="86"/>
-      <c r="N39" s="86"/>
-      <c r="O39" s="86"/>
-      <c r="P39" s="86"/>
-      <c r="Q39" s="86"/>
-      <c r="R39" s="86"/>
-      <c r="S39" s="86"/>
-      <c r="T39" s="86"/>
-      <c r="U39" s="86"/>
-      <c r="V39" s="86"/>
-      <c r="W39" s="87"/>
-      <c r="X39" s="78"/>
-      <c r="Y39" s="79"/>
-      <c r="Z39" s="79"/>
-      <c r="AA39" s="79"/>
-      <c r="AB39" s="80"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="81"/>
+      <c r="M39" s="81"/>
+      <c r="N39" s="81"/>
+      <c r="O39" s="81"/>
+      <c r="P39" s="81"/>
+      <c r="Q39" s="81"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="81"/>
+      <c r="T39" s="81"/>
+      <c r="U39" s="81"/>
+      <c r="V39" s="81"/>
+      <c r="W39" s="82"/>
+      <c r="X39" s="67"/>
+      <c r="Y39" s="78"/>
+      <c r="Z39" s="78"/>
+      <c r="AA39" s="78"/>
+      <c r="AB39" s="68"/>
     </row>
     <row r="40" spans="2:28">
-      <c r="B40" s="40"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="9" t="s">
+      <c r="B40" s="89"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9" t="s">
+      <c r="E40" s="29"/>
+      <c r="F40" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9" t="s">
+      <c r="G40" s="29"/>
+      <c r="H40" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="I40" s="25"/>
-      <c r="J40" s="10" t="s">
+      <c r="I40" s="30"/>
+      <c r="J40" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K40" s="10"/>
-      <c r="L40" s="6" t="s">
+      <c r="K40" s="6"/>
+      <c r="L40" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M40" s="47" t="s">
+      <c r="M40" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="N40" s="47"/>
-      <c r="O40" s="47"/>
-      <c r="P40" s="6" t="s">
+      <c r="N40" s="96"/>
+      <c r="O40" s="96"/>
+      <c r="P40" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="6" t="s">
+      <c r="Q40" s="27"/>
+      <c r="R40" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="S40" s="30" t="s">
+      <c r="S40" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="T40" s="6" t="s">
+      <c r="T40" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="U40" s="7"/>
-      <c r="V40" s="6" t="s">
+      <c r="U40" s="27"/>
+      <c r="V40" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="W40" s="32" t="s">
+      <c r="W40" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="X40" s="81" t="s">
+      <c r="X40" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="Y40" s="82"/>
-      <c r="Z40" s="82"/>
-      <c r="AA40" s="82"/>
-      <c r="AB40" s="83"/>
+      <c r="Y40" s="56"/>
+      <c r="Z40" s="56"/>
+      <c r="AA40" s="56"/>
+      <c r="AB40" s="57"/>
     </row>
     <row r="41" spans="2:28">
-      <c r="B41" s="46"/>
-      <c r="C41" s="49" t="s">
+      <c r="B41" s="95"/>
+      <c r="C41" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="26" t="s">
+      <c r="D41" s="83"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="99"/>
+      <c r="J41" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="27"/>
-      <c r="L41" s="26" t="s">
+      <c r="K41" s="23"/>
+      <c r="L41" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="M41" s="48" t="s">
+      <c r="M41" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="N41" s="48"/>
-      <c r="O41" s="48"/>
-      <c r="P41" s="26" t="s">
+      <c r="N41" s="97"/>
+      <c r="O41" s="97"/>
+      <c r="P41" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="Q41" s="27"/>
-      <c r="R41" s="26" t="s">
+      <c r="Q41" s="23"/>
+      <c r="R41" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="S41" s="31" t="s">
+      <c r="S41" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="T41" s="29" t="s">
+      <c r="T41" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="U41" s="28"/>
-      <c r="V41" s="29" t="s">
+      <c r="U41" s="19"/>
+      <c r="V41" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="W41" s="33" t="s">
+      <c r="W41" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="X41" s="26" t="s">
+      <c r="X41" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="Y41" s="27"/>
-      <c r="Z41" s="33" t="s">
+      <c r="Y41" s="23"/>
+      <c r="Z41" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="AA41" s="34" t="s">
+      <c r="AA41" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="AB41" s="35"/>
+      <c r="AB41" s="84"/>
     </row>
     <row r="42" spans="2:28">
       <c r="B42" s="2" t="s">
@@ -3418,159 +3511,159 @@
       </c>
     </row>
     <row r="43" spans="2:28">
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="100" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="52"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="52"/>
-      <c r="K43" s="52"/>
-      <c r="L43" s="52"/>
-      <c r="M43" s="52"/>
-      <c r="N43" s="52"/>
-      <c r="O43" s="52"/>
-      <c r="P43" s="52"/>
-      <c r="Q43" s="52"/>
-      <c r="R43" s="52"/>
-      <c r="S43" s="52"/>
-      <c r="T43" s="52"/>
-      <c r="U43" s="52"/>
-      <c r="V43" s="52"/>
-      <c r="W43" s="52"/>
-      <c r="X43" s="52"/>
-      <c r="Y43" s="52"/>
-      <c r="Z43" s="52"/>
-      <c r="AA43" s="52"/>
-      <c r="AB43" s="53"/>
+      <c r="C43" s="101"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="101"/>
+      <c r="F43" s="101"/>
+      <c r="G43" s="101"/>
+      <c r="H43" s="101"/>
+      <c r="I43" s="101"/>
+      <c r="J43" s="101"/>
+      <c r="K43" s="101"/>
+      <c r="L43" s="101"/>
+      <c r="M43" s="101"/>
+      <c r="N43" s="101"/>
+      <c r="O43" s="101"/>
+      <c r="P43" s="101"/>
+      <c r="Q43" s="101"/>
+      <c r="R43" s="101"/>
+      <c r="S43" s="101"/>
+      <c r="T43" s="101"/>
+      <c r="U43" s="101"/>
+      <c r="V43" s="101"/>
+      <c r="W43" s="101"/>
+      <c r="X43" s="101"/>
+      <c r="Y43" s="101"/>
+      <c r="Z43" s="101"/>
+      <c r="AA43" s="101"/>
+      <c r="AB43" s="102"/>
     </row>
     <row r="44" spans="2:28">
-      <c r="B44" s="51" t="s">
+      <c r="B44" s="100" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="52"/>
-      <c r="M44" s="52"/>
-      <c r="N44" s="52"/>
-      <c r="O44" s="52"/>
-      <c r="P44" s="52"/>
-      <c r="Q44" s="52"/>
-      <c r="R44" s="52"/>
-      <c r="S44" s="52"/>
-      <c r="T44" s="52"/>
-      <c r="U44" s="52"/>
-      <c r="V44" s="52"/>
-      <c r="W44" s="52"/>
-      <c r="X44" s="52"/>
-      <c r="Y44" s="52"/>
-      <c r="Z44" s="52"/>
-      <c r="AA44" s="52"/>
-      <c r="AB44" s="53"/>
+      <c r="C44" s="101"/>
+      <c r="D44" s="101"/>
+      <c r="E44" s="101"/>
+      <c r="F44" s="101"/>
+      <c r="G44" s="101"/>
+      <c r="H44" s="101"/>
+      <c r="I44" s="101"/>
+      <c r="J44" s="101"/>
+      <c r="K44" s="101"/>
+      <c r="L44" s="101"/>
+      <c r="M44" s="101"/>
+      <c r="N44" s="101"/>
+      <c r="O44" s="101"/>
+      <c r="P44" s="101"/>
+      <c r="Q44" s="101"/>
+      <c r="R44" s="101"/>
+      <c r="S44" s="101"/>
+      <c r="T44" s="101"/>
+      <c r="U44" s="101"/>
+      <c r="V44" s="101"/>
+      <c r="W44" s="101"/>
+      <c r="X44" s="101"/>
+      <c r="Y44" s="101"/>
+      <c r="Z44" s="101"/>
+      <c r="AA44" s="101"/>
+      <c r="AB44" s="102"/>
     </row>
     <row r="45" spans="2:28">
-      <c r="B45" s="51" t="s">
+      <c r="B45" s="100" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="52"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="52"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="52"/>
-      <c r="O45" s="52"/>
-      <c r="P45" s="52"/>
-      <c r="Q45" s="52"/>
-      <c r="R45" s="52"/>
-      <c r="S45" s="52"/>
-      <c r="T45" s="52"/>
-      <c r="U45" s="52"/>
-      <c r="V45" s="52"/>
-      <c r="W45" s="52"/>
-      <c r="X45" s="52"/>
-      <c r="Y45" s="52"/>
-      <c r="Z45" s="52"/>
-      <c r="AA45" s="52"/>
-      <c r="AB45" s="53"/>
+      <c r="C45" s="101"/>
+      <c r="D45" s="101"/>
+      <c r="E45" s="101"/>
+      <c r="F45" s="101"/>
+      <c r="G45" s="101"/>
+      <c r="H45" s="101"/>
+      <c r="I45" s="101"/>
+      <c r="J45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="101"/>
+      <c r="M45" s="101"/>
+      <c r="N45" s="101"/>
+      <c r="O45" s="101"/>
+      <c r="P45" s="101"/>
+      <c r="Q45" s="101"/>
+      <c r="R45" s="101"/>
+      <c r="S45" s="101"/>
+      <c r="T45" s="101"/>
+      <c r="U45" s="101"/>
+      <c r="V45" s="101"/>
+      <c r="W45" s="101"/>
+      <c r="X45" s="101"/>
+      <c r="Y45" s="101"/>
+      <c r="Z45" s="101"/>
+      <c r="AA45" s="101"/>
+      <c r="AB45" s="102"/>
     </row>
     <row r="46" spans="2:28">
-      <c r="B46" s="54" t="s">
+      <c r="B46" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="55"/>
-      <c r="J46" s="55"/>
-      <c r="K46" s="55"/>
-      <c r="L46" s="55"/>
-      <c r="M46" s="55"/>
-      <c r="N46" s="55"/>
-      <c r="O46" s="55"/>
-      <c r="P46" s="55"/>
-      <c r="Q46" s="55"/>
-      <c r="R46" s="55"/>
-      <c r="S46" s="55"/>
-      <c r="T46" s="55"/>
-      <c r="U46" s="55"/>
-      <c r="V46" s="55"/>
-      <c r="W46" s="55"/>
-      <c r="X46" s="55"/>
-      <c r="Y46" s="55"/>
-      <c r="Z46" s="55"/>
-      <c r="AA46" s="55"/>
-      <c r="AB46" s="56"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="104"/>
+      <c r="K46" s="104"/>
+      <c r="L46" s="104"/>
+      <c r="M46" s="104"/>
+      <c r="N46" s="104"/>
+      <c r="O46" s="104"/>
+      <c r="P46" s="104"/>
+      <c r="Q46" s="104"/>
+      <c r="R46" s="104"/>
+      <c r="S46" s="104"/>
+      <c r="T46" s="104"/>
+      <c r="U46" s="104"/>
+      <c r="V46" s="104"/>
+      <c r="W46" s="104"/>
+      <c r="X46" s="104"/>
+      <c r="Y46" s="104"/>
+      <c r="Z46" s="104"/>
+      <c r="AA46" s="104"/>
+      <c r="AB46" s="105"/>
     </row>
     <row r="47" spans="2:28">
-      <c r="B47" s="36" t="s">
+      <c r="B47" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37"/>
-      <c r="I47" s="37"/>
-      <c r="J47" s="37"/>
-      <c r="K47" s="37"/>
-      <c r="L47" s="37"/>
-      <c r="M47" s="37"/>
-      <c r="N47" s="37"/>
-      <c r="O47" s="37"/>
-      <c r="P47" s="37"/>
-      <c r="Q47" s="37"/>
-      <c r="R47" s="37"/>
-      <c r="S47" s="37"/>
-      <c r="T47" s="37"/>
-      <c r="U47" s="37"/>
-      <c r="V47" s="37"/>
-      <c r="W47" s="37"/>
-      <c r="X47" s="37"/>
-      <c r="Y47" s="37"/>
-      <c r="Z47" s="37"/>
-      <c r="AA47" s="37"/>
-      <c r="AB47" s="38"/>
+      <c r="C47" s="86"/>
+      <c r="D47" s="86"/>
+      <c r="E47" s="86"/>
+      <c r="F47" s="86"/>
+      <c r="G47" s="86"/>
+      <c r="H47" s="86"/>
+      <c r="I47" s="86"/>
+      <c r="J47" s="86"/>
+      <c r="K47" s="86"/>
+      <c r="L47" s="86"/>
+      <c r="M47" s="86"/>
+      <c r="N47" s="86"/>
+      <c r="O47" s="86"/>
+      <c r="P47" s="86"/>
+      <c r="Q47" s="86"/>
+      <c r="R47" s="86"/>
+      <c r="S47" s="86"/>
+      <c r="T47" s="86"/>
+      <c r="U47" s="86"/>
+      <c r="V47" s="86"/>
+      <c r="W47" s="86"/>
+      <c r="X47" s="86"/>
+      <c r="Y47" s="86"/>
+      <c r="Z47" s="86"/>
+      <c r="AA47" s="86"/>
+      <c r="AB47" s="87"/>
     </row>
     <row r="48" spans="2:28">
       <c r="B48" s="1" t="s">
@@ -3579,41 +3672,6 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="B1:AB1"/>
-    <mergeCell ref="B2:AB2"/>
-    <mergeCell ref="B3:AB3"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="G5:N5"/>
-    <mergeCell ref="O4:T4"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="U4:Z4"/>
-    <mergeCell ref="U5:AB5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:AB6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="Z7:AB7"/>
-    <mergeCell ref="M7:T7"/>
-    <mergeCell ref="U7:Y7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:W9"/>
-    <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="M8:T8"/>
-    <mergeCell ref="U8:Y8"/>
-    <mergeCell ref="C10:W16"/>
-    <mergeCell ref="AA10:AB16"/>
-    <mergeCell ref="C17:W23"/>
-    <mergeCell ref="AA17:AB23"/>
-    <mergeCell ref="C24:W30"/>
-    <mergeCell ref="AA24:AB30"/>
-    <mergeCell ref="AA31:AB37"/>
-    <mergeCell ref="C38:I39"/>
-    <mergeCell ref="X38:AB39"/>
-    <mergeCell ref="X40:AB40"/>
-    <mergeCell ref="J38:W39"/>
     <mergeCell ref="AA41:AB41"/>
     <mergeCell ref="B47:AB47"/>
     <mergeCell ref="B5:B8"/>
@@ -3630,6 +3688,41 @@
     <mergeCell ref="B45:AB45"/>
     <mergeCell ref="B46:AB46"/>
     <mergeCell ref="C31:W37"/>
+    <mergeCell ref="AA31:AB37"/>
+    <mergeCell ref="C38:I39"/>
+    <mergeCell ref="X38:AB39"/>
+    <mergeCell ref="X40:AB40"/>
+    <mergeCell ref="J38:W39"/>
+    <mergeCell ref="C10:W16"/>
+    <mergeCell ref="AA10:AB16"/>
+    <mergeCell ref="C17:W23"/>
+    <mergeCell ref="AA17:AB23"/>
+    <mergeCell ref="C24:W30"/>
+    <mergeCell ref="AA24:AB30"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:W9"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="M8:T8"/>
+    <mergeCell ref="U8:Y8"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:AB6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="Z7:AB7"/>
+    <mergeCell ref="M7:T7"/>
+    <mergeCell ref="U7:Y7"/>
+    <mergeCell ref="B1:AB1"/>
+    <mergeCell ref="B2:AB2"/>
+    <mergeCell ref="B3:AB3"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G5:N5"/>
+    <mergeCell ref="O4:T4"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="U4:Z4"/>
+    <mergeCell ref="U5:AB5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -3640,7 +3733,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A3521D4-F788-4ECB-8A1A-6C2ED8966189}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
@@ -3694,168 +3787,263 @@
         <v>62</v>
       </c>
     </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
       <c r="B17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="33">
+      <c r="B18" s="124" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="33">
       <c r="A19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>80</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="33">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="33">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="33">
       <c r="A22" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="33">
-      <c r="B23" s="121" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="33">
+        <v>86</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="121" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="33">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="121" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="33">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="121" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="33">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="49.5">
       <c r="A27" t="s">
-        <v>87</v>
-      </c>
-      <c r="B27" s="121" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>96</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="33">
       <c r="A28" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
+        <v>98</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>100</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
+        <v>102</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="49.5">
+        <v>104</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="121" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="33">
+        <v>108</v>
+      </c>
+      <c r="B33" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="121" t="s">
-        <v>97</v>
+        <v>110</v>
+      </c>
+      <c r="B34" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="B35" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>114</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/cha-bio-safety/public/templates/worklog_template.xlsx
+++ b/cha-bio-safety/public/templates/worklog_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21A2DE1A-67EC-47DD-813C-52427B133CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5971F2B-38CE-4854-B5AA-B36CD720660A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="양식" sheetId="2" r:id="rId1"/>
@@ -40,9 +40,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="129">
   <si>
     <t>■ 화재의 예방 및 안전관리에 관한 법률 시행규칙 [별지 제12서식]  </t>
+  </si>
+  <si>
+    <t>[2년간 보관]</t>
   </si>
   <si>
     <t>소방안전관리자 업무 수행 기록표 </t>
@@ -216,7 +219,7 @@
     <t>C4</t>
   </si>
   <si>
-    <t>현재 년 yy</t>
+    <t>현재 년 yyyy</t>
   </si>
   <si>
     <t>E4</t>
@@ -246,28 +249,34 @@
     <t>C10</t>
   </si>
   <si>
-    <t>소화기 - 압력, 약제 상태</t>
-  </si>
-  <si>
-    <t>소화전 - 호스, 관창 상태, 표시등 상태</t>
-  </si>
-  <si>
-    <t>S/P - 밸브 개폐 상태, 압력 상태</t>
-  </si>
-  <si>
-    <t>소방 펌프 - 수동 기동 점검</t>
+    <t>소화기 - 압력 및 약제 상태</t>
+  </si>
+  <si>
+    <t>소화전 - 경종, 표시등 상태, 호스 및 관창 이상유무</t>
+  </si>
+  <si>
+    <t>S/P - 1,2차 압력 상태, 밸브 개폐 상태, 컴프레셔 작동 상태</t>
+  </si>
+  <si>
+    <t>소방 펌프 - 수동 작동 점검, 밸브 개폐 상태, 배관 내 압력 상태</t>
   </si>
   <si>
     <t>C17</t>
   </si>
   <si>
-    <t>방화셔터 - 작동 상태 점검</t>
-  </si>
-  <si>
-    <t>방화문 - 닫힘상태, 도어 체크 상태</t>
-  </si>
-  <si>
-    <t>유도등 - 점등 상태, 전원 상태</t>
+    <t>방화셔터 - 수동 조작 상태, 연동제어기 상태, 장애물 유무 점검</t>
+  </si>
+  <si>
+    <t>방화문 - 닫힘상태, 도어 릴리즈 상태</t>
+  </si>
+  <si>
+    <t>완강기 - 설치 상태, 구성품 상태, 청결 상태</t>
+  </si>
+  <si>
+    <t>배연창 - 작동 상태, 틈새 누수 유무</t>
+  </si>
+  <si>
+    <t>유도등 - 점등 상태, 상용 전원 및 예비 전원 상태</t>
   </si>
   <si>
     <t>C24</t>
@@ -282,7 +291,7 @@
     <t>C31</t>
   </si>
   <si>
-    <t>수신기 정상유지</t>
+    <t>수신기 정상 작동 유지</t>
   </si>
   <si>
     <t>해당 월에 구분 "소방"의 일정이 있으면 기재</t>
@@ -363,7 +372,7 @@
     <t>C40</t>
   </si>
   <si>
-    <t>보고 일시 년 yy</t>
+    <t>보고 일시 년 yyyy</t>
   </si>
   <si>
     <t>E40</t>
@@ -433,7 +442,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,6 +517,15 @@
       <name val="맑은 고딕"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1373,7 +1391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1459,6 +1477,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
@@ -1471,15 +1492,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1740,6 +1752,18 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2105,1381 +2129,1383 @@
     <col min="26" max="26" width="5.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:30">
-      <c r="B1" s="35" t="s">
+    <row r="1" spans="2:30" ht="16.5" customHeight="1">
+      <c r="B1" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="37"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
+      <c r="Q1" s="124"/>
+      <c r="R1" s="124"/>
+      <c r="S1" s="124"/>
+      <c r="T1" s="124"/>
+      <c r="U1" s="124"/>
+      <c r="V1" s="124"/>
+      <c r="W1" s="124"/>
+      <c r="X1" s="124"/>
+      <c r="Y1" s="124"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="125" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB1" s="126"/>
       <c r="AD1" s="4"/>
     </row>
     <row r="2" spans="2:30" ht="26.25">
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="40"/>
+      <c r="B2" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="38"/>
     </row>
     <row r="3" spans="2:30">
-      <c r="B3" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="42"/>
-      <c r="Z3" s="42"/>
-      <c r="AA3" s="42"/>
-      <c r="AB3" s="43"/>
+      <c r="B3" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="40"/>
+      <c r="AB3" s="41"/>
     </row>
     <row r="4" spans="2:30">
       <c r="B4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32" t="s">
-        <v>4</v>
+      <c r="C4" s="32"/>
+      <c r="D4" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33" t="s">
+        <v>5</v>
       </c>
       <c r="I4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="M4" s="32"/>
+      <c r="M4" s="33"/>
       <c r="N4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="O4" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="49"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" s="45" t="s">
         <v>7</v>
       </c>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="50"/>
+      <c r="W4" s="50"/>
+      <c r="X4" s="50"/>
+      <c r="Y4" s="50"/>
+      <c r="Z4" s="50"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="34" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5" spans="2:30">
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="V5" s="51"/>
+      <c r="W5" s="51"/>
+      <c r="X5" s="51"/>
+      <c r="Y5" s="51"/>
+      <c r="Z5" s="51"/>
+      <c r="AA5" s="51"/>
+      <c r="AB5" s="52"/>
+    </row>
+    <row r="6" spans="2:30">
+      <c r="B6" s="87"/>
+      <c r="C6" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
+      <c r="S6" s="54"/>
+      <c r="T6" s="54"/>
+      <c r="U6" s="54"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="54"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="54"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="54"/>
+      <c r="AB6" s="55"/>
+    </row>
+    <row r="7" spans="2:30">
+      <c r="B7" s="87"/>
+      <c r="C7" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="55"/>
+      <c r="U7" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="V7" s="54"/>
+      <c r="W7" s="54"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="57"/>
+      <c r="Z7" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA7" s="54"/>
+      <c r="AB7" s="55"/>
+    </row>
+    <row r="8" spans="2:30">
+      <c r="B8" s="88"/>
+      <c r="C8" s="58">
+        <v>5</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="58">
         <v>8</v>
       </c>
-      <c r="C5" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="V5" s="53"/>
-      <c r="W5" s="53"/>
-      <c r="X5" s="53"/>
-      <c r="Y5" s="53"/>
-      <c r="Z5" s="53"/>
-      <c r="AA5" s="53"/>
-      <c r="AB5" s="54"/>
-    </row>
-    <row r="6" spans="2:30">
-      <c r="B6" s="89"/>
-      <c r="C6" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="56"/>
-      <c r="U6" s="56"/>
-      <c r="V6" s="56"/>
-      <c r="W6" s="56"/>
-      <c r="X6" s="56"/>
-      <c r="Y6" s="56"/>
-      <c r="Z6" s="56"/>
-      <c r="AA6" s="56"/>
-      <c r="AB6" s="57"/>
-    </row>
-    <row r="7" spans="2:30">
-      <c r="B7" s="89"/>
-      <c r="C7" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="57"/>
-      <c r="U7" s="56" t="s">
-        <v>18</v>
-      </c>
-      <c r="V7" s="56"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="56"/>
-      <c r="Y7" s="59"/>
-      <c r="Z7" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA7" s="56"/>
-      <c r="AB7" s="57"/>
-    </row>
-    <row r="8" spans="2:30">
-      <c r="B8" s="90"/>
-      <c r="C8" s="60">
-        <v>5</v>
-      </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="60">
-        <v>8</v>
-      </c>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="62"/>
-      <c r="M8" s="63">
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="60"/>
+      <c r="M8" s="61">
         <v>60557.82</v>
       </c>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
-      <c r="R8" s="64"/>
-      <c r="S8" s="64"/>
-      <c r="T8" s="65"/>
-      <c r="U8" s="64">
+      <c r="N8" s="62"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="62"/>
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="63"/>
+      <c r="U8" s="62">
         <v>6131.87</v>
       </c>
-      <c r="V8" s="64"/>
-      <c r="W8" s="64"/>
-      <c r="X8" s="64"/>
-      <c r="Y8" s="66"/>
-      <c r="Z8" s="60">
+      <c r="V8" s="62"/>
+      <c r="W8" s="62"/>
+      <c r="X8" s="62"/>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="58">
         <v>1</v>
       </c>
-      <c r="AA8" s="61"/>
-      <c r="AB8" s="62"/>
+      <c r="AA8" s="59"/>
+      <c r="AB8" s="60"/>
     </row>
     <row r="9" spans="2:30">
       <c r="B9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="45"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="45"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="44" t="s">
+      <c r="C9" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="Y9" s="45"/>
-      <c r="Z9" s="46"/>
-      <c r="AA9" s="44" t="s">
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="AB9" s="50"/>
+      <c r="Y9" s="43"/>
+      <c r="Z9" s="44"/>
+      <c r="AA9" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB9" s="48"/>
     </row>
     <row r="10" spans="2:30">
-      <c r="B10" s="91" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="106" t="s">
+      <c r="B10" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="107"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="107"/>
-      <c r="L10" s="107"/>
-      <c r="M10" s="107"/>
-      <c r="N10" s="107"/>
-      <c r="O10" s="107"/>
-      <c r="P10" s="107"/>
-      <c r="Q10" s="107"/>
-      <c r="R10" s="107"/>
-      <c r="S10" s="107"/>
-      <c r="T10" s="107"/>
-      <c r="U10" s="107"/>
-      <c r="V10" s="107"/>
-      <c r="W10" s="107"/>
+      <c r="C10" s="104" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="105"/>
+      <c r="O10" s="105"/>
+      <c r="P10" s="105"/>
+      <c r="Q10" s="105"/>
+      <c r="R10" s="105"/>
+      <c r="S10" s="105"/>
+      <c r="T10" s="105"/>
+      <c r="U10" s="105"/>
+      <c r="V10" s="105"/>
+      <c r="W10" s="105"/>
       <c r="X10" s="11"/>
       <c r="Y10" s="12"/>
       <c r="Z10" s="12"/>
-      <c r="AA10" s="116" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB10" s="117"/>
+      <c r="AA10" s="114" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB10" s="115"/>
     </row>
     <row r="11" spans="2:30">
-      <c r="B11" s="92"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="109"/>
-      <c r="E11" s="109"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="109"/>
-      <c r="K11" s="109"/>
-      <c r="L11" s="109"/>
-      <c r="M11" s="109"/>
-      <c r="N11" s="109"/>
-      <c r="O11" s="109"/>
-      <c r="P11" s="109"/>
-      <c r="Q11" s="109"/>
-      <c r="R11" s="109"/>
-      <c r="S11" s="109"/>
-      <c r="T11" s="109"/>
-      <c r="U11" s="109"/>
-      <c r="V11" s="109"/>
-      <c r="W11" s="109"/>
+      <c r="B11" s="90"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="107"/>
+      <c r="L11" s="107"/>
+      <c r="M11" s="107"/>
+      <c r="N11" s="107"/>
+      <c r="O11" s="107"/>
+      <c r="P11" s="107"/>
+      <c r="Q11" s="107"/>
+      <c r="R11" s="107"/>
+      <c r="S11" s="107"/>
+      <c r="T11" s="107"/>
+      <c r="U11" s="107"/>
+      <c r="V11" s="107"/>
+      <c r="W11" s="107"/>
       <c r="X11" s="11"/>
       <c r="Y11" s="12"/>
       <c r="Z11" s="12"/>
-      <c r="AA11" s="118"/>
-      <c r="AB11" s="119"/>
+      <c r="AA11" s="116"/>
+      <c r="AB11" s="117"/>
     </row>
     <row r="12" spans="2:30">
-      <c r="B12" s="92"/>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="111"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="111"/>
-      <c r="P12" s="111"/>
-      <c r="Q12" s="111"/>
-      <c r="R12" s="111"/>
-      <c r="S12" s="111"/>
-      <c r="T12" s="111"/>
-      <c r="U12" s="111"/>
-      <c r="V12" s="111"/>
-      <c r="W12" s="111"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="109"/>
+      <c r="E12" s="109"/>
+      <c r="F12" s="109"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="109"/>
+      <c r="J12" s="109"/>
+      <c r="K12" s="109"/>
+      <c r="L12" s="109"/>
+      <c r="M12" s="109"/>
+      <c r="N12" s="109"/>
+      <c r="O12" s="109"/>
+      <c r="P12" s="109"/>
+      <c r="Q12" s="109"/>
+      <c r="R12" s="109"/>
+      <c r="S12" s="109"/>
+      <c r="T12" s="109"/>
+      <c r="U12" s="109"/>
+      <c r="V12" s="109"/>
+      <c r="W12" s="109"/>
       <c r="X12" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y12" s="12"/>
       <c r="Z12" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA12" s="118"/>
-      <c r="AB12" s="119"/>
+        <v>28</v>
+      </c>
+      <c r="AA12" s="116"/>
+      <c r="AB12" s="117"/>
     </row>
     <row r="13" spans="2:30">
-      <c r="B13" s="92"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="111"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="111"/>
-      <c r="P13" s="111"/>
-      <c r="Q13" s="111"/>
-      <c r="R13" s="111"/>
-      <c r="S13" s="111"/>
-      <c r="T13" s="111"/>
-      <c r="U13" s="111"/>
-      <c r="V13" s="111"/>
-      <c r="W13" s="111"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="109"/>
+      <c r="K13" s="109"/>
+      <c r="L13" s="109"/>
+      <c r="M13" s="109"/>
+      <c r="N13" s="109"/>
+      <c r="O13" s="109"/>
+      <c r="P13" s="109"/>
+      <c r="Q13" s="109"/>
+      <c r="R13" s="109"/>
+      <c r="S13" s="109"/>
+      <c r="T13" s="109"/>
+      <c r="U13" s="109"/>
+      <c r="V13" s="109"/>
+      <c r="W13" s="109"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
-      <c r="AA13" s="118"/>
-      <c r="AB13" s="119"/>
+      <c r="AA13" s="116"/>
+      <c r="AB13" s="117"/>
     </row>
     <row r="14" spans="2:30">
-      <c r="B14" s="92"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="111"/>
-      <c r="L14" s="111"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="111"/>
-      <c r="P14" s="111"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="111"/>
-      <c r="T14" s="111"/>
-      <c r="U14" s="111"/>
-      <c r="V14" s="111"/>
-      <c r="W14" s="111"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="108"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="109"/>
+      <c r="I14" s="109"/>
+      <c r="J14" s="109"/>
+      <c r="K14" s="109"/>
+      <c r="L14" s="109"/>
+      <c r="M14" s="109"/>
+      <c r="N14" s="109"/>
+      <c r="O14" s="109"/>
+      <c r="P14" s="109"/>
+      <c r="Q14" s="109"/>
+      <c r="R14" s="109"/>
+      <c r="S14" s="109"/>
+      <c r="T14" s="109"/>
+      <c r="U14" s="109"/>
+      <c r="V14" s="109"/>
+      <c r="W14" s="109"/>
       <c r="X14" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y14" s="12"/>
       <c r="Z14" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA14" s="118"/>
-      <c r="AB14" s="119"/>
+        <v>29</v>
+      </c>
+      <c r="AA14" s="116"/>
+      <c r="AB14" s="117"/>
     </row>
     <row r="15" spans="2:30">
-      <c r="B15" s="92"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="111"/>
-      <c r="P15" s="111"/>
-      <c r="Q15" s="111"/>
-      <c r="R15" s="111"/>
-      <c r="S15" s="111"/>
-      <c r="T15" s="111"/>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111"/>
-      <c r="W15" s="111"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="109"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="109"/>
+      <c r="K15" s="109"/>
+      <c r="L15" s="109"/>
+      <c r="M15" s="109"/>
+      <c r="N15" s="109"/>
+      <c r="O15" s="109"/>
+      <c r="P15" s="109"/>
+      <c r="Q15" s="109"/>
+      <c r="R15" s="109"/>
+      <c r="S15" s="109"/>
+      <c r="T15" s="109"/>
+      <c r="U15" s="109"/>
+      <c r="V15" s="109"/>
+      <c r="W15" s="109"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="12"/>
       <c r="Z15" s="14"/>
-      <c r="AA15" s="118"/>
-      <c r="AB15" s="119"/>
+      <c r="AA15" s="116"/>
+      <c r="AB15" s="117"/>
     </row>
     <row r="16" spans="2:30">
-      <c r="B16" s="93"/>
-      <c r="C16" s="110"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="111"/>
-      <c r="S16" s="111"/>
-      <c r="T16" s="111"/>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-      <c r="W16" s="111"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="109"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="109"/>
+      <c r="K16" s="109"/>
+      <c r="L16" s="109"/>
+      <c r="M16" s="109"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="109"/>
+      <c r="P16" s="109"/>
+      <c r="Q16" s="109"/>
+      <c r="R16" s="109"/>
+      <c r="S16" s="109"/>
+      <c r="T16" s="109"/>
+      <c r="U16" s="109"/>
+      <c r="V16" s="109"/>
+      <c r="W16" s="109"/>
       <c r="X16" s="15"/>
       <c r="Y16" s="16"/>
       <c r="Z16" s="16"/>
-      <c r="AA16" s="120"/>
-      <c r="AB16" s="121"/>
+      <c r="AA16" s="118"/>
+      <c r="AB16" s="119"/>
     </row>
     <row r="17" spans="2:28">
-      <c r="B17" s="91" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="110" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="111"/>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="111"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="111"/>
-      <c r="P17" s="111"/>
-      <c r="Q17" s="111"/>
-      <c r="R17" s="111"/>
-      <c r="S17" s="111"/>
-      <c r="T17" s="111"/>
-      <c r="U17" s="111"/>
-      <c r="V17" s="111"/>
-      <c r="W17" s="111"/>
+      <c r="B17" s="89" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="108" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="109"/>
+      <c r="E17" s="109"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="109"/>
+      <c r="K17" s="109"/>
+      <c r="L17" s="109"/>
+      <c r="M17" s="109"/>
+      <c r="N17" s="109"/>
+      <c r="O17" s="109"/>
+      <c r="P17" s="109"/>
+      <c r="Q17" s="109"/>
+      <c r="R17" s="109"/>
+      <c r="S17" s="109"/>
+      <c r="T17" s="109"/>
+      <c r="U17" s="109"/>
+      <c r="V17" s="109"/>
+      <c r="W17" s="109"/>
       <c r="X17" s="11"/>
       <c r="Y17" s="12"/>
       <c r="Z17" s="12"/>
-      <c r="AA17" s="116" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB17" s="117"/>
+      <c r="AA17" s="114" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB17" s="115"/>
     </row>
     <row r="18" spans="2:28">
-      <c r="B18" s="92"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="111"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="111"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="111"/>
-      <c r="M18" s="111"/>
-      <c r="N18" s="111"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="111"/>
-      <c r="Q18" s="111"/>
-      <c r="R18" s="111"/>
-      <c r="S18" s="111"/>
-      <c r="T18" s="111"/>
-      <c r="U18" s="111"/>
-      <c r="V18" s="111"/>
-      <c r="W18" s="111"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="109"/>
+      <c r="E18" s="109"/>
+      <c r="F18" s="109"/>
+      <c r="G18" s="109"/>
+      <c r="H18" s="109"/>
+      <c r="I18" s="109"/>
+      <c r="J18" s="109"/>
+      <c r="K18" s="109"/>
+      <c r="L18" s="109"/>
+      <c r="M18" s="109"/>
+      <c r="N18" s="109"/>
+      <c r="O18" s="109"/>
+      <c r="P18" s="109"/>
+      <c r="Q18" s="109"/>
+      <c r="R18" s="109"/>
+      <c r="S18" s="109"/>
+      <c r="T18" s="109"/>
+      <c r="U18" s="109"/>
+      <c r="V18" s="109"/>
+      <c r="W18" s="109"/>
       <c r="X18" s="11"/>
       <c r="Y18" s="12"/>
       <c r="Z18" s="12"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="119"/>
+      <c r="AA18" s="116"/>
+      <c r="AB18" s="117"/>
     </row>
     <row r="19" spans="2:28">
-      <c r="B19" s="92"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="111"/>
-      <c r="M19" s="111"/>
-      <c r="N19" s="111"/>
-      <c r="O19" s="111"/>
-      <c r="P19" s="111"/>
-      <c r="Q19" s="111"/>
-      <c r="R19" s="111"/>
-      <c r="S19" s="111"/>
-      <c r="T19" s="111"/>
-      <c r="U19" s="111"/>
-      <c r="V19" s="111"/>
-      <c r="W19" s="111"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="109"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="109"/>
+      <c r="G19" s="109"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="109"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="109"/>
+      <c r="M19" s="109"/>
+      <c r="N19" s="109"/>
+      <c r="O19" s="109"/>
+      <c r="P19" s="109"/>
+      <c r="Q19" s="109"/>
+      <c r="R19" s="109"/>
+      <c r="S19" s="109"/>
+      <c r="T19" s="109"/>
+      <c r="U19" s="109"/>
+      <c r="V19" s="109"/>
+      <c r="W19" s="109"/>
       <c r="X19" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y19" s="12"/>
       <c r="Z19" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA19" s="118"/>
-      <c r="AB19" s="119"/>
+        <v>28</v>
+      </c>
+      <c r="AA19" s="116"/>
+      <c r="AB19" s="117"/>
     </row>
     <row r="20" spans="2:28">
-      <c r="B20" s="92"/>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="111"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="111"/>
-      <c r="N20" s="111"/>
-      <c r="O20" s="111"/>
-      <c r="P20" s="111"/>
-      <c r="Q20" s="111"/>
-      <c r="R20" s="111"/>
-      <c r="S20" s="111"/>
-      <c r="T20" s="111"/>
-      <c r="U20" s="111"/>
-      <c r="V20" s="111"/>
-      <c r="W20" s="111"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="109"/>
+      <c r="E20" s="109"/>
+      <c r="F20" s="109"/>
+      <c r="G20" s="109"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="109"/>
+      <c r="P20" s="109"/>
+      <c r="Q20" s="109"/>
+      <c r="R20" s="109"/>
+      <c r="S20" s="109"/>
+      <c r="T20" s="109"/>
+      <c r="U20" s="109"/>
+      <c r="V20" s="109"/>
+      <c r="W20" s="109"/>
       <c r="X20" s="13"/>
       <c r="Y20" s="12"/>
       <c r="Z20" s="12"/>
-      <c r="AA20" s="118"/>
-      <c r="AB20" s="119"/>
+      <c r="AA20" s="116"/>
+      <c r="AB20" s="117"/>
     </row>
     <row r="21" spans="2:28">
-      <c r="B21" s="92"/>
-      <c r="C21" s="110"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="111"/>
-      <c r="N21" s="111"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="111"/>
-      <c r="Q21" s="111"/>
-      <c r="R21" s="111"/>
-      <c r="S21" s="111"/>
-      <c r="T21" s="111"/>
-      <c r="U21" s="111"/>
-      <c r="V21" s="111"/>
-      <c r="W21" s="111"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="109"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="109"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="109"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
+      <c r="U21" s="109"/>
+      <c r="V21" s="109"/>
+      <c r="W21" s="109"/>
       <c r="X21" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y21" s="12"/>
       <c r="Z21" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA21" s="118"/>
-      <c r="AB21" s="119"/>
+        <v>29</v>
+      </c>
+      <c r="AA21" s="116"/>
+      <c r="AB21" s="117"/>
     </row>
     <row r="22" spans="2:28">
-      <c r="B22" s="92"/>
-      <c r="C22" s="110"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="111"/>
-      <c r="N22" s="111"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="111"/>
-      <c r="Q22" s="111"/>
-      <c r="R22" s="111"/>
-      <c r="S22" s="111"/>
-      <c r="T22" s="111"/>
-      <c r="U22" s="111"/>
-      <c r="V22" s="111"/>
-      <c r="W22" s="111"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="109"/>
+      <c r="E22" s="109"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="109"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="109"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="109"/>
+      <c r="N22" s="109"/>
+      <c r="O22" s="109"/>
+      <c r="P22" s="109"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="109"/>
+      <c r="S22" s="109"/>
+      <c r="T22" s="109"/>
+      <c r="U22" s="109"/>
+      <c r="V22" s="109"/>
+      <c r="W22" s="109"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="14"/>
-      <c r="AA22" s="118"/>
-      <c r="AB22" s="119"/>
+      <c r="AA22" s="116"/>
+      <c r="AB22" s="117"/>
     </row>
     <row r="23" spans="2:28">
-      <c r="B23" s="93"/>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="111"/>
-      <c r="N23" s="111"/>
-      <c r="O23" s="111"/>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="111"/>
-      <c r="S23" s="111"/>
-      <c r="T23" s="111"/>
-      <c r="U23" s="111"/>
-      <c r="V23" s="111"/>
-      <c r="W23" s="111"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="109"/>
+      <c r="E23" s="109"/>
+      <c r="F23" s="109"/>
+      <c r="G23" s="109"/>
+      <c r="H23" s="109"/>
+      <c r="I23" s="109"/>
+      <c r="J23" s="109"/>
+      <c r="K23" s="109"/>
+      <c r="L23" s="109"/>
+      <c r="M23" s="109"/>
+      <c r="N23" s="109"/>
+      <c r="O23" s="109"/>
+      <c r="P23" s="109"/>
+      <c r="Q23" s="109"/>
+      <c r="R23" s="109"/>
+      <c r="S23" s="109"/>
+      <c r="T23" s="109"/>
+      <c r="U23" s="109"/>
+      <c r="V23" s="109"/>
+      <c r="W23" s="109"/>
       <c r="X23" s="15"/>
       <c r="Y23" s="16"/>
       <c r="Z23" s="16"/>
-      <c r="AA23" s="120"/>
-      <c r="AB23" s="121"/>
+      <c r="AA23" s="118"/>
+      <c r="AB23" s="119"/>
     </row>
     <row r="24" spans="2:28">
-      <c r="B24" s="91" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="110" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="111"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
-      <c r="W24" s="111"/>
+      <c r="B24" s="89" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="108" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="109"/>
+      <c r="G24" s="109"/>
+      <c r="H24" s="109"/>
+      <c r="I24" s="109"/>
+      <c r="J24" s="109"/>
+      <c r="K24" s="109"/>
+      <c r="L24" s="109"/>
+      <c r="M24" s="109"/>
+      <c r="N24" s="109"/>
+      <c r="O24" s="109"/>
+      <c r="P24" s="109"/>
+      <c r="Q24" s="109"/>
+      <c r="R24" s="109"/>
+      <c r="S24" s="109"/>
+      <c r="T24" s="109"/>
+      <c r="U24" s="109"/>
+      <c r="V24" s="109"/>
+      <c r="W24" s="109"/>
       <c r="X24" s="11"/>
       <c r="Y24" s="12"/>
       <c r="Z24" s="12"/>
-      <c r="AA24" s="116" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB24" s="117"/>
+      <c r="AA24" s="114" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB24" s="115"/>
     </row>
     <row r="25" spans="2:28">
-      <c r="B25" s="92"/>
-      <c r="C25" s="110"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="111"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="111"/>
-      <c r="R25" s="111"/>
-      <c r="S25" s="111"/>
-      <c r="T25" s="111"/>
-      <c r="U25" s="111"/>
-      <c r="V25" s="111"/>
-      <c r="W25" s="111"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="109"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="109"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="109"/>
+      <c r="R25" s="109"/>
+      <c r="S25" s="109"/>
+      <c r="T25" s="109"/>
+      <c r="U25" s="109"/>
+      <c r="V25" s="109"/>
+      <c r="W25" s="109"/>
       <c r="X25" s="11"/>
       <c r="Y25" s="12"/>
       <c r="Z25" s="12"/>
-      <c r="AA25" s="118"/>
-      <c r="AB25" s="119"/>
+      <c r="AA25" s="116"/>
+      <c r="AB25" s="117"/>
     </row>
     <row r="26" spans="2:28">
-      <c r="B26" s="92"/>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="111"/>
-      <c r="L26" s="111"/>
-      <c r="M26" s="111"/>
-      <c r="N26" s="111"/>
-      <c r="O26" s="111"/>
-      <c r="P26" s="111"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="111"/>
-      <c r="S26" s="111"/>
-      <c r="T26" s="111"/>
-      <c r="U26" s="111"/>
-      <c r="V26" s="111"/>
-      <c r="W26" s="111"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="109"/>
+      <c r="E26" s="109"/>
+      <c r="F26" s="109"/>
+      <c r="G26" s="109"/>
+      <c r="H26" s="109"/>
+      <c r="I26" s="109"/>
+      <c r="J26" s="109"/>
+      <c r="K26" s="109"/>
+      <c r="L26" s="109"/>
+      <c r="M26" s="109"/>
+      <c r="N26" s="109"/>
+      <c r="O26" s="109"/>
+      <c r="P26" s="109"/>
+      <c r="Q26" s="109"/>
+      <c r="R26" s="109"/>
+      <c r="S26" s="109"/>
+      <c r="T26" s="109"/>
+      <c r="U26" s="109"/>
+      <c r="V26" s="109"/>
+      <c r="W26" s="109"/>
       <c r="X26" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y26" s="12"/>
       <c r="Z26" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA26" s="118"/>
-      <c r="AB26" s="119"/>
+        <v>28</v>
+      </c>
+      <c r="AA26" s="116"/>
+      <c r="AB26" s="117"/>
     </row>
     <row r="27" spans="2:28">
-      <c r="B27" s="92"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="111"/>
-      <c r="N27" s="111"/>
-      <c r="O27" s="111"/>
-      <c r="P27" s="111"/>
-      <c r="Q27" s="111"/>
-      <c r="R27" s="111"/>
-      <c r="S27" s="111"/>
-      <c r="T27" s="111"/>
-      <c r="U27" s="111"/>
-      <c r="V27" s="111"/>
-      <c r="W27" s="111"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="109"/>
+      <c r="J27" s="109"/>
+      <c r="K27" s="109"/>
+      <c r="L27" s="109"/>
+      <c r="M27" s="109"/>
+      <c r="N27" s="109"/>
+      <c r="O27" s="109"/>
+      <c r="P27" s="109"/>
+      <c r="Q27" s="109"/>
+      <c r="R27" s="109"/>
+      <c r="S27" s="109"/>
+      <c r="T27" s="109"/>
+      <c r="U27" s="109"/>
+      <c r="V27" s="109"/>
+      <c r="W27" s="109"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="12"/>
       <c r="Z27" s="12"/>
-      <c r="AA27" s="118"/>
-      <c r="AB27" s="119"/>
+      <c r="AA27" s="116"/>
+      <c r="AB27" s="117"/>
     </row>
     <row r="28" spans="2:28">
-      <c r="B28" s="92"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="111"/>
-      <c r="N28" s="111"/>
-      <c r="O28" s="111"/>
-      <c r="P28" s="111"/>
-      <c r="Q28" s="111"/>
-      <c r="R28" s="111"/>
-      <c r="S28" s="111"/>
-      <c r="T28" s="111"/>
-      <c r="U28" s="111"/>
-      <c r="V28" s="111"/>
-      <c r="W28" s="111"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="109"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="109"/>
+      <c r="I28" s="109"/>
+      <c r="J28" s="109"/>
+      <c r="K28" s="109"/>
+      <c r="L28" s="109"/>
+      <c r="M28" s="109"/>
+      <c r="N28" s="109"/>
+      <c r="O28" s="109"/>
+      <c r="P28" s="109"/>
+      <c r="Q28" s="109"/>
+      <c r="R28" s="109"/>
+      <c r="S28" s="109"/>
+      <c r="T28" s="109"/>
+      <c r="U28" s="109"/>
+      <c r="V28" s="109"/>
+      <c r="W28" s="109"/>
       <c r="X28" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y28" s="12"/>
       <c r="Z28" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA28" s="118"/>
-      <c r="AB28" s="119"/>
+        <v>29</v>
+      </c>
+      <c r="AA28" s="116"/>
+      <c r="AB28" s="117"/>
     </row>
     <row r="29" spans="2:28">
-      <c r="B29" s="92"/>
-      <c r="C29" s="110"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="111"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="111"/>
-      <c r="N29" s="111"/>
-      <c r="O29" s="111"/>
-      <c r="P29" s="111"/>
-      <c r="Q29" s="111"/>
-      <c r="R29" s="111"/>
-      <c r="S29" s="111"/>
-      <c r="T29" s="111"/>
-      <c r="U29" s="111"/>
-      <c r="V29" s="111"/>
-      <c r="W29" s="111"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="109"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="109"/>
+      <c r="H29" s="109"/>
+      <c r="I29" s="109"/>
+      <c r="J29" s="109"/>
+      <c r="K29" s="109"/>
+      <c r="L29" s="109"/>
+      <c r="M29" s="109"/>
+      <c r="N29" s="109"/>
+      <c r="O29" s="109"/>
+      <c r="P29" s="109"/>
+      <c r="Q29" s="109"/>
+      <c r="R29" s="109"/>
+      <c r="S29" s="109"/>
+      <c r="T29" s="109"/>
+      <c r="U29" s="109"/>
+      <c r="V29" s="109"/>
+      <c r="W29" s="109"/>
       <c r="X29" s="13"/>
       <c r="Y29" s="12"/>
       <c r="Z29" s="14"/>
-      <c r="AA29" s="118"/>
-      <c r="AB29" s="119"/>
+      <c r="AA29" s="116"/>
+      <c r="AB29" s="117"/>
     </row>
     <row r="30" spans="2:28">
-      <c r="B30" s="93"/>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="111"/>
-      <c r="F30" s="111"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="111"/>
-      <c r="I30" s="111"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="111"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="111"/>
-      <c r="N30" s="111"/>
-      <c r="O30" s="111"/>
-      <c r="P30" s="111"/>
-      <c r="Q30" s="111"/>
-      <c r="R30" s="111"/>
-      <c r="S30" s="111"/>
-      <c r="T30" s="111"/>
-      <c r="U30" s="111"/>
-      <c r="V30" s="111"/>
-      <c r="W30" s="111"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="109"/>
+      <c r="F30" s="109"/>
+      <c r="G30" s="109"/>
+      <c r="H30" s="109"/>
+      <c r="I30" s="109"/>
+      <c r="J30" s="109"/>
+      <c r="K30" s="109"/>
+      <c r="L30" s="109"/>
+      <c r="M30" s="109"/>
+      <c r="N30" s="109"/>
+      <c r="O30" s="109"/>
+      <c r="P30" s="109"/>
+      <c r="Q30" s="109"/>
+      <c r="R30" s="109"/>
+      <c r="S30" s="109"/>
+      <c r="T30" s="109"/>
+      <c r="U30" s="109"/>
+      <c r="V30" s="109"/>
+      <c r="W30" s="109"/>
       <c r="X30" s="15"/>
       <c r="Y30" s="16"/>
       <c r="Z30" s="16"/>
-      <c r="AA30" s="120"/>
-      <c r="AB30" s="121"/>
+      <c r="AA30" s="118"/>
+      <c r="AB30" s="119"/>
     </row>
     <row r="31" spans="2:28">
-      <c r="B31" s="91" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="110" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="111"/>
-      <c r="E31" s="111"/>
-      <c r="F31" s="111"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="111"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="111"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="111"/>
-      <c r="N31" s="111"/>
-      <c r="O31" s="111"/>
-      <c r="P31" s="111"/>
-      <c r="Q31" s="111"/>
-      <c r="R31" s="111"/>
-      <c r="S31" s="111"/>
-      <c r="T31" s="111"/>
-      <c r="U31" s="111"/>
-      <c r="V31" s="111"/>
-      <c r="W31" s="111"/>
+      <c r="B31" s="89" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="108" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="109"/>
+      <c r="G31" s="109"/>
+      <c r="H31" s="109"/>
+      <c r="I31" s="109"/>
+      <c r="J31" s="109"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
+      <c r="M31" s="109"/>
+      <c r="N31" s="109"/>
+      <c r="O31" s="109"/>
+      <c r="P31" s="109"/>
+      <c r="Q31" s="109"/>
+      <c r="R31" s="109"/>
+      <c r="S31" s="109"/>
+      <c r="T31" s="109"/>
+      <c r="U31" s="109"/>
+      <c r="V31" s="109"/>
+      <c r="W31" s="109"/>
       <c r="X31" s="11"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="6"/>
-      <c r="AA31" s="116" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB31" s="117"/>
+      <c r="AA31" s="114" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB31" s="115"/>
     </row>
     <row r="32" spans="2:28">
-      <c r="B32" s="92"/>
-      <c r="C32" s="110"/>
-      <c r="D32" s="111"/>
-      <c r="E32" s="111"/>
-      <c r="F32" s="111"/>
-      <c r="G32" s="111"/>
-      <c r="H32" s="111"/>
-      <c r="I32" s="111"/>
-      <c r="J32" s="111"/>
-      <c r="K32" s="111"/>
-      <c r="L32" s="111"/>
-      <c r="M32" s="111"/>
-      <c r="N32" s="111"/>
-      <c r="O32" s="111"/>
-      <c r="P32" s="111"/>
-      <c r="Q32" s="111"/>
-      <c r="R32" s="111"/>
-      <c r="S32" s="111"/>
-      <c r="T32" s="111"/>
-      <c r="U32" s="111"/>
-      <c r="V32" s="111"/>
-      <c r="W32" s="111"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="108"/>
+      <c r="D32" s="109"/>
+      <c r="E32" s="109"/>
+      <c r="F32" s="109"/>
+      <c r="G32" s="109"/>
+      <c r="H32" s="109"/>
+      <c r="I32" s="109"/>
+      <c r="J32" s="109"/>
+      <c r="K32" s="109"/>
+      <c r="L32" s="109"/>
+      <c r="M32" s="109"/>
+      <c r="N32" s="109"/>
+      <c r="O32" s="109"/>
+      <c r="P32" s="109"/>
+      <c r="Q32" s="109"/>
+      <c r="R32" s="109"/>
+      <c r="S32" s="109"/>
+      <c r="T32" s="109"/>
+      <c r="U32" s="109"/>
+      <c r="V32" s="109"/>
+      <c r="W32" s="109"/>
       <c r="X32" s="11"/>
       <c r="Y32" s="6"/>
       <c r="Z32" s="6"/>
-      <c r="AA32" s="118"/>
-      <c r="AB32" s="119"/>
+      <c r="AA32" s="116"/>
+      <c r="AB32" s="117"/>
     </row>
     <row r="33" spans="2:28">
-      <c r="B33" s="92"/>
-      <c r="C33" s="110"/>
-      <c r="D33" s="111"/>
-      <c r="E33" s="111"/>
-      <c r="F33" s="111"/>
-      <c r="G33" s="111"/>
-      <c r="H33" s="111"/>
-      <c r="I33" s="111"/>
-      <c r="J33" s="111"/>
-      <c r="K33" s="111"/>
-      <c r="L33" s="111"/>
-      <c r="M33" s="111"/>
-      <c r="N33" s="111"/>
-      <c r="O33" s="111"/>
-      <c r="P33" s="111"/>
-      <c r="Q33" s="111"/>
-      <c r="R33" s="111"/>
-      <c r="S33" s="111"/>
-      <c r="T33" s="111"/>
-      <c r="U33" s="111"/>
-      <c r="V33" s="111"/>
-      <c r="W33" s="111"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="109"/>
+      <c r="G33" s="109"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="109"/>
+      <c r="J33" s="109"/>
+      <c r="K33" s="109"/>
+      <c r="L33" s="109"/>
+      <c r="M33" s="109"/>
+      <c r="N33" s="109"/>
+      <c r="O33" s="109"/>
+      <c r="P33" s="109"/>
+      <c r="Q33" s="109"/>
+      <c r="R33" s="109"/>
+      <c r="S33" s="109"/>
+      <c r="T33" s="109"/>
+      <c r="U33" s="109"/>
+      <c r="V33" s="109"/>
+      <c r="W33" s="109"/>
       <c r="X33" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y33" s="6"/>
       <c r="Z33" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA33" s="118"/>
-      <c r="AB33" s="119"/>
+        <v>28</v>
+      </c>
+      <c r="AA33" s="116"/>
+      <c r="AB33" s="117"/>
     </row>
     <row r="34" spans="2:28">
-      <c r="B34" s="92"/>
-      <c r="C34" s="110"/>
-      <c r="D34" s="111"/>
-      <c r="E34" s="111"/>
-      <c r="F34" s="111"/>
-      <c r="G34" s="111"/>
-      <c r="H34" s="111"/>
-      <c r="I34" s="111"/>
-      <c r="J34" s="111"/>
-      <c r="K34" s="111"/>
-      <c r="L34" s="111"/>
-      <c r="M34" s="111"/>
-      <c r="N34" s="111"/>
-      <c r="O34" s="111"/>
-      <c r="P34" s="111"/>
-      <c r="Q34" s="111"/>
-      <c r="R34" s="111"/>
-      <c r="S34" s="111"/>
-      <c r="T34" s="111"/>
-      <c r="U34" s="111"/>
-      <c r="V34" s="111"/>
-      <c r="W34" s="111"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="108"/>
+      <c r="D34" s="109"/>
+      <c r="E34" s="109"/>
+      <c r="F34" s="109"/>
+      <c r="G34" s="109"/>
+      <c r="H34" s="109"/>
+      <c r="I34" s="109"/>
+      <c r="J34" s="109"/>
+      <c r="K34" s="109"/>
+      <c r="L34" s="109"/>
+      <c r="M34" s="109"/>
+      <c r="N34" s="109"/>
+      <c r="O34" s="109"/>
+      <c r="P34" s="109"/>
+      <c r="Q34" s="109"/>
+      <c r="R34" s="109"/>
+      <c r="S34" s="109"/>
+      <c r="T34" s="109"/>
+      <c r="U34" s="109"/>
+      <c r="V34" s="109"/>
+      <c r="W34" s="109"/>
       <c r="X34" s="13"/>
       <c r="Y34" s="6"/>
       <c r="Z34" s="6"/>
-      <c r="AA34" s="118"/>
-      <c r="AB34" s="119"/>
+      <c r="AA34" s="116"/>
+      <c r="AB34" s="117"/>
     </row>
     <row r="35" spans="2:28">
-      <c r="B35" s="92"/>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="111"/>
-      <c r="S35" s="111"/>
-      <c r="T35" s="111"/>
-      <c r="U35" s="111"/>
-      <c r="V35" s="111"/>
-      <c r="W35" s="111"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="108"/>
+      <c r="D35" s="109"/>
+      <c r="E35" s="109"/>
+      <c r="F35" s="109"/>
+      <c r="G35" s="109"/>
+      <c r="H35" s="109"/>
+      <c r="I35" s="109"/>
+      <c r="J35" s="109"/>
+      <c r="K35" s="109"/>
+      <c r="L35" s="109"/>
+      <c r="M35" s="109"/>
+      <c r="N35" s="109"/>
+      <c r="O35" s="109"/>
+      <c r="P35" s="109"/>
+      <c r="Q35" s="109"/>
+      <c r="R35" s="109"/>
+      <c r="S35" s="109"/>
+      <c r="T35" s="109"/>
+      <c r="U35" s="109"/>
+      <c r="V35" s="109"/>
+      <c r="W35" s="109"/>
       <c r="X35" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y35" s="6"/>
       <c r="Z35" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA35" s="118"/>
-      <c r="AB35" s="119"/>
+        <v>29</v>
+      </c>
+      <c r="AA35" s="116"/>
+      <c r="AB35" s="117"/>
     </row>
     <row r="36" spans="2:28">
-      <c r="B36" s="92"/>
-      <c r="C36" s="112"/>
-      <c r="D36" s="113"/>
-      <c r="E36" s="113"/>
-      <c r="F36" s="113"/>
-      <c r="G36" s="113"/>
-      <c r="H36" s="113"/>
-      <c r="I36" s="113"/>
-      <c r="J36" s="113"/>
-      <c r="K36" s="113"/>
-      <c r="L36" s="113"/>
-      <c r="M36" s="113"/>
-      <c r="N36" s="113"/>
-      <c r="O36" s="113"/>
-      <c r="P36" s="113"/>
-      <c r="Q36" s="113"/>
-      <c r="R36" s="113"/>
-      <c r="S36" s="113"/>
-      <c r="T36" s="113"/>
-      <c r="U36" s="113"/>
-      <c r="V36" s="113"/>
-      <c r="W36" s="113"/>
+      <c r="B36" s="90"/>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="111"/>
+      <c r="F36" s="111"/>
+      <c r="G36" s="111"/>
+      <c r="H36" s="111"/>
+      <c r="I36" s="111"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="111"/>
+      <c r="L36" s="111"/>
+      <c r="M36" s="111"/>
+      <c r="N36" s="111"/>
+      <c r="O36" s="111"/>
+      <c r="P36" s="111"/>
+      <c r="Q36" s="111"/>
+      <c r="R36" s="111"/>
+      <c r="S36" s="111"/>
+      <c r="T36" s="111"/>
+      <c r="U36" s="111"/>
+      <c r="V36" s="111"/>
+      <c r="W36" s="111"/>
       <c r="X36" s="13"/>
       <c r="Y36" s="6"/>
       <c r="Z36" s="17"/>
-      <c r="AA36" s="118"/>
-      <c r="AB36" s="119"/>
+      <c r="AA36" s="116"/>
+      <c r="AB36" s="117"/>
     </row>
     <row r="37" spans="2:28">
-      <c r="B37" s="94"/>
-      <c r="C37" s="114"/>
-      <c r="D37" s="115"/>
-      <c r="E37" s="115"/>
-      <c r="F37" s="115"/>
-      <c r="G37" s="115"/>
-      <c r="H37" s="115"/>
-      <c r="I37" s="115"/>
-      <c r="J37" s="115"/>
-      <c r="K37" s="115"/>
-      <c r="L37" s="115"/>
-      <c r="M37" s="115"/>
-      <c r="N37" s="115"/>
-      <c r="O37" s="115"/>
-      <c r="P37" s="115"/>
-      <c r="Q37" s="115"/>
-      <c r="R37" s="115"/>
-      <c r="S37" s="115"/>
-      <c r="T37" s="115"/>
-      <c r="U37" s="115"/>
-      <c r="V37" s="115"/>
-      <c r="W37" s="115"/>
+      <c r="B37" s="92"/>
+      <c r="C37" s="112"/>
+      <c r="D37" s="113"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="113"/>
+      <c r="G37" s="113"/>
+      <c r="H37" s="113"/>
+      <c r="I37" s="113"/>
+      <c r="J37" s="113"/>
+      <c r="K37" s="113"/>
+      <c r="L37" s="113"/>
+      <c r="M37" s="113"/>
+      <c r="N37" s="113"/>
+      <c r="O37" s="113"/>
+      <c r="P37" s="113"/>
+      <c r="Q37" s="113"/>
+      <c r="R37" s="113"/>
+      <c r="S37" s="113"/>
+      <c r="T37" s="113"/>
+      <c r="U37" s="113"/>
+      <c r="V37" s="113"/>
+      <c r="W37" s="113"/>
       <c r="X37" s="11"/>
       <c r="Y37" s="6"/>
       <c r="Z37" s="6"/>
-      <c r="AA37" s="122"/>
-      <c r="AB37" s="123"/>
+      <c r="AA37" s="120"/>
+      <c r="AB37" s="121"/>
     </row>
     <row r="38" spans="2:28">
-      <c r="B38" s="88" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="69" t="s">
+      <c r="B38" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="75" t="s">
+      <c r="C38" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="K38" s="76"/>
-      <c r="L38" s="76"/>
-      <c r="M38" s="76"/>
-      <c r="N38" s="76"/>
-      <c r="O38" s="76"/>
-      <c r="P38" s="76"/>
-      <c r="Q38" s="76"/>
-      <c r="R38" s="76"/>
-      <c r="S38" s="76"/>
-      <c r="T38" s="76"/>
-      <c r="U38" s="76"/>
-      <c r="V38" s="76"/>
-      <c r="W38" s="79"/>
-      <c r="X38" s="75" t="s">
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="Y38" s="76"/>
-      <c r="Z38" s="76"/>
-      <c r="AA38" s="76"/>
-      <c r="AB38" s="77"/>
+      <c r="K38" s="74"/>
+      <c r="L38" s="74"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="74"/>
+      <c r="P38" s="74"/>
+      <c r="Q38" s="74"/>
+      <c r="R38" s="74"/>
+      <c r="S38" s="74"/>
+      <c r="T38" s="74"/>
+      <c r="U38" s="74"/>
+      <c r="V38" s="74"/>
+      <c r="W38" s="77"/>
+      <c r="X38" s="73" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y38" s="74"/>
+      <c r="Z38" s="74"/>
+      <c r="AA38" s="74"/>
+      <c r="AB38" s="75"/>
     </row>
     <row r="39" spans="2:28">
-      <c r="B39" s="89"/>
-      <c r="C39" s="72"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="74"/>
-      <c r="J39" s="80"/>
-      <c r="K39" s="81"/>
-      <c r="L39" s="81"/>
-      <c r="M39" s="81"/>
-      <c r="N39" s="81"/>
-      <c r="O39" s="81"/>
-      <c r="P39" s="81"/>
-      <c r="Q39" s="81"/>
-      <c r="R39" s="81"/>
-      <c r="S39" s="81"/>
-      <c r="T39" s="81"/>
-      <c r="U39" s="81"/>
-      <c r="V39" s="81"/>
-      <c r="W39" s="82"/>
-      <c r="X39" s="67"/>
-      <c r="Y39" s="78"/>
-      <c r="Z39" s="78"/>
-      <c r="AA39" s="78"/>
-      <c r="AB39" s="68"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="72"/>
+      <c r="J39" s="78"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="79"/>
+      <c r="M39" s="79"/>
+      <c r="N39" s="79"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="79"/>
+      <c r="Q39" s="79"/>
+      <c r="R39" s="79"/>
+      <c r="S39" s="79"/>
+      <c r="T39" s="79"/>
+      <c r="U39" s="79"/>
+      <c r="V39" s="79"/>
+      <c r="W39" s="80"/>
+      <c r="X39" s="65"/>
+      <c r="Y39" s="76"/>
+      <c r="Z39" s="76"/>
+      <c r="AA39" s="76"/>
+      <c r="AB39" s="66"/>
     </row>
     <row r="40" spans="2:28">
-      <c r="B40" s="89"/>
+      <c r="B40" s="87"/>
       <c r="C40" s="28"/>
       <c r="D40" s="29" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" s="29"/>
       <c r="F40" s="29" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G40" s="29"/>
       <c r="H40" s="29" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I40" s="30"/>
       <c r="J40" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="M40" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="N40" s="96"/>
-      <c r="O40" s="96"/>
+      <c r="M40" s="94" t="s">
+        <v>38</v>
+      </c>
+      <c r="N40" s="94"/>
+      <c r="O40" s="94"/>
       <c r="P40" s="26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q40" s="27"/>
       <c r="R40" s="26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S40" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T40" s="26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U40" s="27"/>
       <c r="V40" s="26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W40" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="X40" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="Y40" s="56"/>
-      <c r="Z40" s="56"/>
-      <c r="AA40" s="56"/>
-      <c r="AB40" s="57"/>
+      <c r="X40" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y40" s="54"/>
+      <c r="Z40" s="54"/>
+      <c r="AA40" s="54"/>
+      <c r="AB40" s="55"/>
     </row>
     <row r="41" spans="2:28">
-      <c r="B41" s="95"/>
-      <c r="C41" s="98" t="s">
-        <v>41</v>
-      </c>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="99"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="96" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="97"/>
       <c r="J41" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K41" s="23"/>
       <c r="L41" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="M41" s="97" t="s">
-        <v>42</v>
-      </c>
-      <c r="N41" s="97"/>
-      <c r="O41" s="97"/>
+        <v>37</v>
+      </c>
+      <c r="M41" s="95" t="s">
+        <v>43</v>
+      </c>
+      <c r="N41" s="95"/>
+      <c r="O41" s="95"/>
       <c r="P41" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q41" s="23"/>
       <c r="R41" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S41" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U41" s="19"/>
       <c r="V41" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W41" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X41" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y41" s="23"/>
       <c r="Z41" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA41" s="83" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB41" s="84"/>
+        <v>46</v>
+      </c>
+      <c r="AA41" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB41" s="82"/>
     </row>
     <row r="42" spans="2:28">
       <c r="B42" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -3507,171 +3533,171 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3"/>
       <c r="AB42" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="2:28">
-      <c r="B43" s="100" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43" s="101"/>
-      <c r="D43" s="101"/>
-      <c r="E43" s="101"/>
-      <c r="F43" s="101"/>
-      <c r="G43" s="101"/>
-      <c r="H43" s="101"/>
-      <c r="I43" s="101"/>
-      <c r="J43" s="101"/>
-      <c r="K43" s="101"/>
-      <c r="L43" s="101"/>
-      <c r="M43" s="101"/>
-      <c r="N43" s="101"/>
-      <c r="O43" s="101"/>
-      <c r="P43" s="101"/>
-      <c r="Q43" s="101"/>
-      <c r="R43" s="101"/>
-      <c r="S43" s="101"/>
-      <c r="T43" s="101"/>
-      <c r="U43" s="101"/>
-      <c r="V43" s="101"/>
-      <c r="W43" s="101"/>
-      <c r="X43" s="101"/>
-      <c r="Y43" s="101"/>
-      <c r="Z43" s="101"/>
-      <c r="AA43" s="101"/>
-      <c r="AB43" s="102"/>
+      <c r="B43" s="98" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="99"/>
+      <c r="R43" s="99"/>
+      <c r="S43" s="99"/>
+      <c r="T43" s="99"/>
+      <c r="U43" s="99"/>
+      <c r="V43" s="99"/>
+      <c r="W43" s="99"/>
+      <c r="X43" s="99"/>
+      <c r="Y43" s="99"/>
+      <c r="Z43" s="99"/>
+      <c r="AA43" s="99"/>
+      <c r="AB43" s="100"/>
     </row>
     <row r="44" spans="2:28">
-      <c r="B44" s="100" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" s="101"/>
-      <c r="D44" s="101"/>
-      <c r="E44" s="101"/>
-      <c r="F44" s="101"/>
-      <c r="G44" s="101"/>
-      <c r="H44" s="101"/>
-      <c r="I44" s="101"/>
-      <c r="J44" s="101"/>
-      <c r="K44" s="101"/>
-      <c r="L44" s="101"/>
-      <c r="M44" s="101"/>
-      <c r="N44" s="101"/>
-      <c r="O44" s="101"/>
-      <c r="P44" s="101"/>
-      <c r="Q44" s="101"/>
-      <c r="R44" s="101"/>
-      <c r="S44" s="101"/>
-      <c r="T44" s="101"/>
-      <c r="U44" s="101"/>
-      <c r="V44" s="101"/>
-      <c r="W44" s="101"/>
-      <c r="X44" s="101"/>
-      <c r="Y44" s="101"/>
-      <c r="Z44" s="101"/>
-      <c r="AA44" s="101"/>
-      <c r="AB44" s="102"/>
+      <c r="B44" s="98" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="99"/>
+      <c r="I44" s="99"/>
+      <c r="J44" s="99"/>
+      <c r="K44" s="99"/>
+      <c r="L44" s="99"/>
+      <c r="M44" s="99"/>
+      <c r="N44" s="99"/>
+      <c r="O44" s="99"/>
+      <c r="P44" s="99"/>
+      <c r="Q44" s="99"/>
+      <c r="R44" s="99"/>
+      <c r="S44" s="99"/>
+      <c r="T44" s="99"/>
+      <c r="U44" s="99"/>
+      <c r="V44" s="99"/>
+      <c r="W44" s="99"/>
+      <c r="X44" s="99"/>
+      <c r="Y44" s="99"/>
+      <c r="Z44" s="99"/>
+      <c r="AA44" s="99"/>
+      <c r="AB44" s="100"/>
     </row>
     <row r="45" spans="2:28">
-      <c r="B45" s="100" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="101"/>
-      <c r="D45" s="101"/>
-      <c r="E45" s="101"/>
-      <c r="F45" s="101"/>
-      <c r="G45" s="101"/>
-      <c r="H45" s="101"/>
-      <c r="I45" s="101"/>
-      <c r="J45" s="101"/>
-      <c r="K45" s="101"/>
-      <c r="L45" s="101"/>
-      <c r="M45" s="101"/>
-      <c r="N45" s="101"/>
-      <c r="O45" s="101"/>
-      <c r="P45" s="101"/>
-      <c r="Q45" s="101"/>
-      <c r="R45" s="101"/>
-      <c r="S45" s="101"/>
-      <c r="T45" s="101"/>
-      <c r="U45" s="101"/>
-      <c r="V45" s="101"/>
-      <c r="W45" s="101"/>
-      <c r="X45" s="101"/>
-      <c r="Y45" s="101"/>
-      <c r="Z45" s="101"/>
-      <c r="AA45" s="101"/>
-      <c r="AB45" s="102"/>
+      <c r="B45" s="98" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
+      <c r="F45" s="99"/>
+      <c r="G45" s="99"/>
+      <c r="H45" s="99"/>
+      <c r="I45" s="99"/>
+      <c r="J45" s="99"/>
+      <c r="K45" s="99"/>
+      <c r="L45" s="99"/>
+      <c r="M45" s="99"/>
+      <c r="N45" s="99"/>
+      <c r="O45" s="99"/>
+      <c r="P45" s="99"/>
+      <c r="Q45" s="99"/>
+      <c r="R45" s="99"/>
+      <c r="S45" s="99"/>
+      <c r="T45" s="99"/>
+      <c r="U45" s="99"/>
+      <c r="V45" s="99"/>
+      <c r="W45" s="99"/>
+      <c r="X45" s="99"/>
+      <c r="Y45" s="99"/>
+      <c r="Z45" s="99"/>
+      <c r="AA45" s="99"/>
+      <c r="AB45" s="100"/>
     </row>
     <row r="46" spans="2:28">
-      <c r="B46" s="103" t="s">
-        <v>51</v>
-      </c>
-      <c r="C46" s="104"/>
-      <c r="D46" s="104"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="104"/>
-      <c r="K46" s="104"/>
-      <c r="L46" s="104"/>
-      <c r="M46" s="104"/>
-      <c r="N46" s="104"/>
-      <c r="O46" s="104"/>
-      <c r="P46" s="104"/>
-      <c r="Q46" s="104"/>
-      <c r="R46" s="104"/>
-      <c r="S46" s="104"/>
-      <c r="T46" s="104"/>
-      <c r="U46" s="104"/>
-      <c r="V46" s="104"/>
-      <c r="W46" s="104"/>
-      <c r="X46" s="104"/>
-      <c r="Y46" s="104"/>
-      <c r="Z46" s="104"/>
-      <c r="AA46" s="104"/>
-      <c r="AB46" s="105"/>
+      <c r="B46" s="101" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="102"/>
+      <c r="D46" s="102"/>
+      <c r="E46" s="102"/>
+      <c r="F46" s="102"/>
+      <c r="G46" s="102"/>
+      <c r="H46" s="102"/>
+      <c r="I46" s="102"/>
+      <c r="J46" s="102"/>
+      <c r="K46" s="102"/>
+      <c r="L46" s="102"/>
+      <c r="M46" s="102"/>
+      <c r="N46" s="102"/>
+      <c r="O46" s="102"/>
+      <c r="P46" s="102"/>
+      <c r="Q46" s="102"/>
+      <c r="R46" s="102"/>
+      <c r="S46" s="102"/>
+      <c r="T46" s="102"/>
+      <c r="U46" s="102"/>
+      <c r="V46" s="102"/>
+      <c r="W46" s="102"/>
+      <c r="X46" s="102"/>
+      <c r="Y46" s="102"/>
+      <c r="Z46" s="102"/>
+      <c r="AA46" s="102"/>
+      <c r="AB46" s="103"/>
     </row>
     <row r="47" spans="2:28">
-      <c r="B47" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="C47" s="86"/>
-      <c r="D47" s="86"/>
-      <c r="E47" s="86"/>
-      <c r="F47" s="86"/>
-      <c r="G47" s="86"/>
-      <c r="H47" s="86"/>
-      <c r="I47" s="86"/>
-      <c r="J47" s="86"/>
-      <c r="K47" s="86"/>
-      <c r="L47" s="86"/>
-      <c r="M47" s="86"/>
-      <c r="N47" s="86"/>
-      <c r="O47" s="86"/>
-      <c r="P47" s="86"/>
-      <c r="Q47" s="86"/>
-      <c r="R47" s="86"/>
-      <c r="S47" s="86"/>
-      <c r="T47" s="86"/>
-      <c r="U47" s="86"/>
-      <c r="V47" s="86"/>
-      <c r="W47" s="86"/>
-      <c r="X47" s="86"/>
-      <c r="Y47" s="86"/>
-      <c r="Z47" s="86"/>
-      <c r="AA47" s="86"/>
-      <c r="AB47" s="87"/>
+      <c r="B47" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="84"/>
+      <c r="D47" s="84"/>
+      <c r="E47" s="84"/>
+      <c r="F47" s="84"/>
+      <c r="G47" s="84"/>
+      <c r="H47" s="84"/>
+      <c r="I47" s="84"/>
+      <c r="J47" s="84"/>
+      <c r="K47" s="84"/>
+      <c r="L47" s="84"/>
+      <c r="M47" s="84"/>
+      <c r="N47" s="84"/>
+      <c r="O47" s="84"/>
+      <c r="P47" s="84"/>
+      <c r="Q47" s="84"/>
+      <c r="R47" s="84"/>
+      <c r="S47" s="84"/>
+      <c r="T47" s="84"/>
+      <c r="U47" s="84"/>
+      <c r="V47" s="84"/>
+      <c r="W47" s="84"/>
+      <c r="X47" s="84"/>
+      <c r="Y47" s="84"/>
+      <c r="Z47" s="84"/>
+      <c r="AA47" s="84"/>
+      <c r="AB47" s="85"/>
     </row>
     <row r="48" spans="2:28">
       <c r="B48" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="52">
     <mergeCell ref="AA41:AB41"/>
     <mergeCell ref="B47:AB47"/>
     <mergeCell ref="B5:B8"/>
@@ -3714,7 +3740,6 @@
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="M7:T7"/>
     <mergeCell ref="U7:Y7"/>
-    <mergeCell ref="B1:AB1"/>
     <mergeCell ref="B2:AB2"/>
     <mergeCell ref="B3:AB3"/>
     <mergeCell ref="C5:F5"/>
@@ -3723,6 +3748,8 @@
     <mergeCell ref="O5:T5"/>
     <mergeCell ref="U4:Z4"/>
     <mergeCell ref="U5:AB5"/>
+    <mergeCell ref="B1:Y1"/>
+    <mergeCell ref="AA1:AB1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -3733,39 +3760,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A3521D4-F788-4ECB-8A1A-6C2ED8966189}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3773,73 +3800,70 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="B9" t="s">
-        <v>67</v>
+      <c r="B9" s="35" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="B10" t="s">
-        <v>68</v>
+      <c r="B10" s="35" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
       <c r="B15" t="s">
         <v>75</v>
       </c>
@@ -3857,193 +3881,206 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="33">
-      <c r="B18" s="124" t="s">
+    <row r="18" spans="1:2">
+      <c r="B18" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="33">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="33">
-      <c r="A20" t="s">
+    <row r="20" spans="1:2">
+      <c r="B20" s="122" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="34" t="s">
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="33">
-      <c r="A21" t="s">
+      <c r="B21" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="34" t="s">
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="33">
-      <c r="A22" t="s">
+      <c r="B22" s="35" t="s">
         <v>86</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="35" t="s">
         <v>88</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="35" t="s">
         <v>90</v>
-      </c>
-      <c r="B24" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" t="s">
         <v>92</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" t="s">
         <v>94</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="49.5">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>96</v>
       </c>
-      <c r="B27" s="34" t="s">
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="33">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>98</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="35" t="s">
         <v>100</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="35" t="s">
         <v>102</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="35" t="s">
         <v>104</v>
-      </c>
-      <c r="B31" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="35" t="s">
         <v>106</v>
-      </c>
-      <c r="B32" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" t="s">
         <v>108</v>
-      </c>
-      <c r="B33" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" t="s">
         <v>110</v>
-      </c>
-      <c r="B34" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" t="s">
         <v>112</v>
-      </c>
-      <c r="B35" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" t="s">
         <v>114</v>
-      </c>
-      <c r="B36" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" t="s">
         <v>116</v>
-      </c>
-      <c r="B37" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" t="s">
         <v>118</v>
-      </c>
-      <c r="B38" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" t="s">
         <v>120</v>
-      </c>
-      <c r="B39" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" t="s">
         <v>122</v>
-      </c>
-      <c r="B40" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" t="s">
         <v>124</v>
       </c>
-      <c r="B41" t="s">
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
         <v>125</v>
+      </c>
+      <c r="B42" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
